--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692900</v>
+        <v>122692893</v>
       </c>
       <c r="B2" t="n">
         <v>78660</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736268</v>
+        <v>735982</v>
       </c>
       <c r="R2" t="n">
-        <v>7413074</v>
+        <v>7413229</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692888</v>
+        <v>122692899</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736141</v>
+        <v>736253</v>
       </c>
       <c r="R3" t="n">
-        <v>7413344</v>
+        <v>7413096</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692864</v>
+        <v>122692862</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736292</v>
+        <v>735946</v>
       </c>
       <c r="R4" t="n">
-        <v>7412983</v>
+        <v>7413485</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -956,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692865</v>
+        <v>122692906</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>82447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736116</v>
+        <v>736295</v>
       </c>
       <c r="R5" t="n">
-        <v>7412997</v>
+        <v>7412988</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1066,6 +1070,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692874</v>
+        <v>122692877</v>
       </c>
       <c r="B6" t="n">
-        <v>78397</v>
+        <v>57533</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>103022</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736203</v>
+        <v>736170</v>
       </c>
       <c r="R6" t="n">
-        <v>7412940</v>
+        <v>7413160</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,7 +1173,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1187,7 +1191,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692915</v>
+        <v>122692897</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1227,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736095</v>
+        <v>736248</v>
       </c>
       <c r="R7" t="n">
-        <v>7413383</v>
+        <v>7413169</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1271,7 +1275,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692867</v>
+        <v>122692856</v>
       </c>
       <c r="B8" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1306,21 +1309,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736165</v>
+        <v>736114</v>
       </c>
       <c r="R8" t="n">
-        <v>7413161</v>
+        <v>7412934</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692853</v>
+        <v>122692908</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>56594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1404,25 +1407,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736120</v>
+        <v>736202</v>
       </c>
       <c r="R9" t="n">
-        <v>7412935</v>
+        <v>7413250</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1468,6 +1471,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692880</v>
+        <v>122692874</v>
       </c>
       <c r="B10" t="n">
-        <v>78396</v>
+        <v>78397</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1510,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736205</v>
+        <v>736203</v>
       </c>
       <c r="R10" t="n">
-        <v>7412943</v>
+        <v>7412940</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1597,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692891</v>
+        <v>122692859</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,25 +1617,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736029</v>
+        <v>736141</v>
       </c>
       <c r="R11" t="n">
-        <v>7413135</v>
+        <v>7413297</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692866</v>
+        <v>122692868</v>
       </c>
       <c r="B12" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,21 +1723,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736167</v>
+        <v>736267</v>
       </c>
       <c r="R12" t="n">
-        <v>7413025</v>
+        <v>7413160</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1775,6 +1783,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,7 +1814,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692902</v>
+        <v>122692903</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1841,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736287</v>
+        <v>736135</v>
       </c>
       <c r="R13" t="n">
-        <v>7412989</v>
+        <v>7412970</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1903,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692890</v>
+        <v>122692879</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1943,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736078</v>
+        <v>736253</v>
       </c>
       <c r="R14" t="n">
-        <v>7413098</v>
+        <v>7413052</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1987,6 +2000,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2005,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692905</v>
+        <v>122692880</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,21 +2035,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736175</v>
+        <v>736205</v>
       </c>
       <c r="R15" t="n">
-        <v>7413127</v>
+        <v>7412943</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2089,6 +2103,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2107,7 +2122,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692916</v>
+        <v>122692888</v>
       </c>
       <c r="B16" t="n">
         <v>78660</v>
@@ -2147,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736092</v>
+        <v>736141</v>
       </c>
       <c r="R16" t="n">
-        <v>7413264</v>
+        <v>7413344</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692850</v>
+        <v>122692865</v>
       </c>
       <c r="B17" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736028</v>
+        <v>736116</v>
       </c>
       <c r="R17" t="n">
-        <v>7413218</v>
+        <v>7412997</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692914</v>
+        <v>122692864</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736141</v>
+        <v>736292</v>
       </c>
       <c r="R18" t="n">
-        <v>7413319</v>
+        <v>7412983</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2396,7 +2411,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2415,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692860</v>
+        <v>122692853</v>
       </c>
       <c r="B19" t="n">
-        <v>56594</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2427,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2455,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736132</v>
+        <v>736120</v>
       </c>
       <c r="R19" t="n">
-        <v>7412974</v>
+        <v>7412935</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2491,11 +2505,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2522,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692906</v>
+        <v>122692891</v>
       </c>
       <c r="B20" t="n">
-        <v>82447</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736295</v>
+        <v>736029</v>
       </c>
       <c r="R20" t="n">
-        <v>7412988</v>
+        <v>7413135</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2606,7 +2615,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2625,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692903</v>
+        <v>122692876</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>57495</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2637,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2665,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736135</v>
+        <v>736253</v>
       </c>
       <c r="R21" t="n">
-        <v>7412970</v>
+        <v>7413052</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2727,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692886</v>
+        <v>122692855</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,37 +2751,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736116</v>
+        <v>736124</v>
       </c>
       <c r="R22" t="n">
-        <v>7412995</v>
+        <v>7412945</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2814,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2833,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692895</v>
+        <v>122692905</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2873,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736222</v>
+        <v>736175</v>
       </c>
       <c r="R23" t="n">
-        <v>7413197</v>
+        <v>7413127</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2935,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692877</v>
+        <v>122692914</v>
       </c>
       <c r="B24" t="n">
-        <v>57533</v>
+        <v>78660</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2975,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736170</v>
+        <v>736141</v>
       </c>
       <c r="R24" t="n">
-        <v>7413160</v>
+        <v>7413319</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3019,6 +3023,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,7 +3042,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692897</v>
+        <v>122692895</v>
       </c>
       <c r="B25" t="n">
         <v>78660</v>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736248</v>
+        <v>736222</v>
       </c>
       <c r="R25" t="n">
-        <v>7413169</v>
+        <v>7413197</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3144,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692904</v>
+        <v>122692851</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,21 +3160,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3184,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736171</v>
+        <v>736115</v>
       </c>
       <c r="R26" t="n">
-        <v>7412886</v>
+        <v>7412928</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692876</v>
+        <v>122692915</v>
       </c>
       <c r="B27" t="n">
-        <v>57495</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3258,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3286,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736253</v>
+        <v>736095</v>
       </c>
       <c r="R27" t="n">
-        <v>7413052</v>
+        <v>7413383</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3325,6 +3330,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3349,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692868</v>
+        <v>122692892</v>
       </c>
       <c r="B28" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,21 +3365,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736267</v>
+        <v>735982</v>
       </c>
       <c r="R28" t="n">
-        <v>7413160</v>
+        <v>7413172</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3419,11 +3425,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3450,10 +3451,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692851</v>
+        <v>122692916</v>
       </c>
       <c r="B29" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,21 +3467,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3490,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736115</v>
+        <v>736092</v>
       </c>
       <c r="R29" t="n">
-        <v>7412928</v>
+        <v>7413264</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3534,6 +3535,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3552,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692908</v>
+        <v>122692901</v>
       </c>
       <c r="B30" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3564,25 +3566,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3592,10 +3594,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736202</v>
+        <v>736256</v>
       </c>
       <c r="R30" t="n">
-        <v>7413250</v>
+        <v>7413074</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3628,11 +3630,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3659,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692861</v>
+        <v>122692913</v>
       </c>
       <c r="B31" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3671,25 +3668,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3699,10 +3696,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736142</v>
+        <v>736262</v>
       </c>
       <c r="R31" t="n">
-        <v>7413297</v>
+        <v>7413022</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3743,6 +3740,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692879</v>
+        <v>122692902</v>
       </c>
       <c r="B32" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,21 +3775,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736253</v>
+        <v>736287</v>
       </c>
       <c r="R32" t="n">
-        <v>7413052</v>
+        <v>7412989</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3845,7 +3843,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3864,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692863</v>
+        <v>122692890</v>
       </c>
       <c r="B33" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3876,25 +3873,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736167</v>
+        <v>736078</v>
       </c>
       <c r="R33" t="n">
-        <v>7413243</v>
+        <v>7413098</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3940,11 +3937,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3971,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692852</v>
+        <v>122692860</v>
       </c>
       <c r="B34" t="n">
-        <v>57384</v>
+        <v>56594</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3983,25 +3975,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4011,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736126</v>
+        <v>736132</v>
       </c>
       <c r="R34" t="n">
-        <v>7412904</v>
+        <v>7412974</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4047,6 +4039,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4073,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692899</v>
+        <v>122692900</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -4113,10 +4110,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736253</v>
+        <v>736268</v>
       </c>
       <c r="R35" t="n">
-        <v>7413096</v>
+        <v>7413074</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4175,10 +4172,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692896</v>
+        <v>122692867</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4191,21 +4188,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4215,10 +4212,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736227</v>
+        <v>736165</v>
       </c>
       <c r="R36" t="n">
-        <v>7413172</v>
+        <v>7413161</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4277,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692859</v>
+        <v>122692861</v>
       </c>
       <c r="B37" t="n">
         <v>56594</v>
@@ -4317,7 +4314,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736141</v>
+        <v>736142</v>
       </c>
       <c r="R37" t="n">
         <v>7413297</v>
@@ -4379,10 +4376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692856</v>
+        <v>122692886</v>
       </c>
       <c r="B38" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4395,34 +4392,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736114</v>
+        <v>736116</v>
       </c>
       <c r="R38" t="n">
-        <v>7412934</v>
+        <v>7412995</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4463,6 +4463,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4482,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692889</v>
+        <v>122692852</v>
       </c>
       <c r="B39" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4497,21 +4498,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736006</v>
+        <v>736126</v>
       </c>
       <c r="R39" t="n">
-        <v>7413410</v>
+        <v>7412904</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4565,7 +4566,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692862</v>
+        <v>122692863</v>
       </c>
       <c r="B40" t="n">
         <v>56594</v>
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735946</v>
+        <v>736167</v>
       </c>
       <c r="R40" t="n">
-        <v>7413485</v>
+        <v>7413243</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Tjädertall</t>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4691,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692892</v>
+        <v>122692866</v>
       </c>
       <c r="B41" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735982</v>
+        <v>736167</v>
       </c>
       <c r="R41" t="n">
-        <v>7413172</v>
+        <v>7413025</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692893</v>
+        <v>122692904</v>
       </c>
       <c r="B42" t="n">
         <v>78660</v>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735982</v>
+        <v>736171</v>
       </c>
       <c r="R42" t="n">
-        <v>7413229</v>
+        <v>7412886</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4895,7 +4895,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692901</v>
+        <v>122692887</v>
       </c>
       <c r="B43" t="n">
         <v>78660</v>
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736256</v>
+        <v>735969</v>
       </c>
       <c r="R43" t="n">
-        <v>7413074</v>
+        <v>7413433</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4979,6 +4979,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4997,7 +4998,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692913</v>
+        <v>122692889</v>
       </c>
       <c r="B44" t="n">
         <v>78660</v>
@@ -5037,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736262</v>
+        <v>736006</v>
       </c>
       <c r="R44" t="n">
-        <v>7413022</v>
+        <v>7413410</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5100,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692887</v>
+        <v>122692850</v>
       </c>
       <c r="B45" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5116,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>735969</v>
+        <v>736028</v>
       </c>
       <c r="R45" t="n">
-        <v>7413433</v>
+        <v>7413218</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5184,7 +5185,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692855</v>
+        <v>122692896</v>
       </c>
       <c r="B46" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736124</v>
+        <v>736227</v>
       </c>
       <c r="R46" t="n">
-        <v>7412945</v>
+        <v>7413172</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692893</v>
+        <v>122692877</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>57533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735982</v>
+        <v>736170</v>
       </c>
       <c r="R2" t="n">
-        <v>7413229</v>
+        <v>7413160</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692899</v>
+        <v>122692893</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736253</v>
+        <v>735982</v>
       </c>
       <c r="R3" t="n">
-        <v>7413096</v>
+        <v>7413229</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692862</v>
+        <v>122692905</v>
       </c>
       <c r="B4" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735946</v>
+        <v>736175</v>
       </c>
       <c r="R4" t="n">
-        <v>7413485</v>
+        <v>7413127</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692906</v>
+        <v>122692908</v>
       </c>
       <c r="B5" t="n">
-        <v>82447</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736295</v>
+        <v>736202</v>
       </c>
       <c r="R5" t="n">
-        <v>7412988</v>
+        <v>7413250</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1064,13 +1059,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692877</v>
+        <v>122692889</v>
       </c>
       <c r="B6" t="n">
-        <v>57533</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736170</v>
+        <v>736006</v>
       </c>
       <c r="R6" t="n">
-        <v>7413160</v>
+        <v>7413410</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1173,6 +1172,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692897</v>
+        <v>122692891</v>
       </c>
       <c r="B7" t="n">
         <v>78660</v>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736248</v>
+        <v>736029</v>
       </c>
       <c r="R7" t="n">
-        <v>7413169</v>
+        <v>7413135</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692856</v>
+        <v>122692906</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>82447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,21 +1309,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736114</v>
+        <v>736295</v>
       </c>
       <c r="R8" t="n">
-        <v>7412934</v>
+        <v>7412988</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1377,6 +1377,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1395,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692908</v>
+        <v>122692895</v>
       </c>
       <c r="B9" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,25 +1408,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736202</v>
+        <v>736222</v>
       </c>
       <c r="R9" t="n">
-        <v>7413250</v>
+        <v>7413197</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1471,11 +1472,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1502,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692874</v>
+        <v>122692867</v>
       </c>
       <c r="B10" t="n">
-        <v>78397</v>
+        <v>57537</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,21 +1514,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736203</v>
+        <v>736165</v>
       </c>
       <c r="R10" t="n">
-        <v>7412940</v>
+        <v>7413161</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1586,7 +1582,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1605,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692859</v>
+        <v>122692874</v>
       </c>
       <c r="B11" t="n">
-        <v>56594</v>
+        <v>78397</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,25 +1612,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736141</v>
+        <v>736203</v>
       </c>
       <c r="R11" t="n">
-        <v>7413297</v>
+        <v>7412940</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1689,6 +1684,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1707,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692868</v>
+        <v>122692879</v>
       </c>
       <c r="B12" t="n">
-        <v>57400</v>
+        <v>78396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736267</v>
+        <v>736253</v>
       </c>
       <c r="R12" t="n">
-        <v>7413160</v>
+        <v>7413052</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1785,17 +1781,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1814,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692903</v>
+        <v>122692896</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1854,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736135</v>
+        <v>736227</v>
       </c>
       <c r="R13" t="n">
-        <v>7412970</v>
+        <v>7413172</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1916,7 +1908,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692879</v>
+        <v>122692880</v>
       </c>
       <c r="B14" t="n">
         <v>78396</v>
@@ -1956,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736253</v>
+        <v>736205</v>
       </c>
       <c r="R14" t="n">
-        <v>7413052</v>
+        <v>7412943</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2019,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692880</v>
+        <v>122692859</v>
       </c>
       <c r="B15" t="n">
-        <v>78396</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736205</v>
+        <v>736141</v>
       </c>
       <c r="R15" t="n">
-        <v>7412943</v>
+        <v>7413297</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,7 +2095,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2122,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692888</v>
+        <v>122692856</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2162,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736141</v>
+        <v>736114</v>
       </c>
       <c r="R16" t="n">
-        <v>7413344</v>
+        <v>7412934</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2206,7 +2197,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2225,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692865</v>
+        <v>122692863</v>
       </c>
       <c r="B17" t="n">
-        <v>57537</v>
+        <v>56594</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736116</v>
+        <v>736167</v>
       </c>
       <c r="R17" t="n">
-        <v>7412997</v>
+        <v>7413243</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2301,6 +2291,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692864</v>
+        <v>122692860</v>
       </c>
       <c r="B18" t="n">
-        <v>57537</v>
+        <v>56594</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736292</v>
+        <v>736132</v>
       </c>
       <c r="R18" t="n">
-        <v>7412983</v>
+        <v>7412974</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2403,6 +2398,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692853</v>
+        <v>122692892</v>
       </c>
       <c r="B19" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736120</v>
+        <v>735982</v>
       </c>
       <c r="R19" t="n">
-        <v>7412935</v>
+        <v>7413172</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692891</v>
+        <v>122692850</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736029</v>
+        <v>736028</v>
       </c>
       <c r="R20" t="n">
-        <v>7413135</v>
+        <v>7413218</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692876</v>
+        <v>122692864</v>
       </c>
       <c r="B21" t="n">
-        <v>57495</v>
+        <v>57537</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736253</v>
+        <v>736292</v>
       </c>
       <c r="R21" t="n">
-        <v>7413052</v>
+        <v>7412983</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692855</v>
+        <v>122692897</v>
       </c>
       <c r="B22" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736124</v>
+        <v>736248</v>
       </c>
       <c r="R22" t="n">
-        <v>7412945</v>
+        <v>7413169</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692905</v>
+        <v>122692888</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736175</v>
+        <v>736141</v>
       </c>
       <c r="R23" t="n">
-        <v>7413127</v>
+        <v>7413344</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2921,6 +2921,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2939,7 +2940,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692914</v>
+        <v>122692903</v>
       </c>
       <c r="B24" t="n">
         <v>78660</v>
@@ -2979,10 +2980,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736141</v>
+        <v>736135</v>
       </c>
       <c r="R24" t="n">
-        <v>7413319</v>
+        <v>7412970</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3023,7 +3024,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692895</v>
+        <v>122692861</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3054,25 +3054,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736222</v>
+        <v>736142</v>
       </c>
       <c r="R25" t="n">
-        <v>7413197</v>
+        <v>7413297</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692851</v>
+        <v>122692865</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,21 +3160,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736115</v>
+        <v>736116</v>
       </c>
       <c r="R26" t="n">
-        <v>7412928</v>
+        <v>7412997</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692892</v>
+        <v>122692899</v>
       </c>
       <c r="B28" t="n">
         <v>78660</v>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735982</v>
+        <v>736253</v>
       </c>
       <c r="R28" t="n">
-        <v>7413172</v>
+        <v>7413096</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692916</v>
+        <v>122692855</v>
       </c>
       <c r="B29" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736092</v>
+        <v>736124</v>
       </c>
       <c r="R29" t="n">
-        <v>7413264</v>
+        <v>7412945</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3535,7 +3535,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3554,7 +3553,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692901</v>
+        <v>122692914</v>
       </c>
       <c r="B30" t="n">
         <v>78660</v>
@@ -3594,10 +3593,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736256</v>
+        <v>736141</v>
       </c>
       <c r="R30" t="n">
-        <v>7413074</v>
+        <v>7413319</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3638,6 +3637,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3656,7 +3656,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692913</v>
+        <v>122692887</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736262</v>
+        <v>735969</v>
       </c>
       <c r="R31" t="n">
-        <v>7413022</v>
+        <v>7413433</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692860</v>
+        <v>122692868</v>
       </c>
       <c r="B34" t="n">
-        <v>56594</v>
+        <v>57400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,25 +3975,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736132</v>
+        <v>736267</v>
       </c>
       <c r="R34" t="n">
-        <v>7412974</v>
+        <v>7413160</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Tjädertall</t>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692900</v>
+        <v>122692886</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -4104,16 +4104,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736268</v>
+        <v>736116</v>
       </c>
       <c r="R35" t="n">
-        <v>7413074</v>
+        <v>7412995</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4154,6 +4157,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4176,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692867</v>
+        <v>122692900</v>
       </c>
       <c r="B36" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4188,21 +4192,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4212,10 +4216,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736165</v>
+        <v>736268</v>
       </c>
       <c r="R36" t="n">
-        <v>7413161</v>
+        <v>7413074</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4274,7 +4278,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692861</v>
+        <v>122692862</v>
       </c>
       <c r="B37" t="n">
         <v>56594</v>
@@ -4314,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736142</v>
+        <v>735946</v>
       </c>
       <c r="R37" t="n">
-        <v>7413297</v>
+        <v>7413485</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4350,6 +4354,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4376,7 +4385,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692886</v>
+        <v>122692904</v>
       </c>
       <c r="B38" t="n">
         <v>78660</v>
@@ -4410,19 +4419,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736116</v>
+        <v>736171</v>
       </c>
       <c r="R38" t="n">
-        <v>7412995</v>
+        <v>7412886</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4463,7 +4469,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4482,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692852</v>
+        <v>122692876</v>
       </c>
       <c r="B39" t="n">
-        <v>57384</v>
+        <v>57495</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,20 +4499,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4522,10 +4527,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736126</v>
+        <v>736253</v>
       </c>
       <c r="R39" t="n">
-        <v>7412904</v>
+        <v>7413052</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4584,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692863</v>
+        <v>122692916</v>
       </c>
       <c r="B40" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4596,25 +4601,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4624,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736167</v>
+        <v>736092</v>
       </c>
       <c r="R40" t="n">
-        <v>7413243</v>
+        <v>7413264</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4662,17 +4667,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692866</v>
+        <v>122692901</v>
       </c>
       <c r="B41" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4707,21 +4708,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4731,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736167</v>
+        <v>736256</v>
       </c>
       <c r="R41" t="n">
-        <v>7413025</v>
+        <v>7413074</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4793,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692904</v>
+        <v>122692866</v>
       </c>
       <c r="B42" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4809,21 +4810,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4833,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736171</v>
+        <v>736167</v>
       </c>
       <c r="R42" t="n">
-        <v>7412886</v>
+        <v>7413025</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4895,10 +4896,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692887</v>
+        <v>122692852</v>
       </c>
       <c r="B43" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4911,21 +4912,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4935,10 +4936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>735969</v>
+        <v>736126</v>
       </c>
       <c r="R43" t="n">
-        <v>7413433</v>
+        <v>7412904</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4979,7 +4980,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692889</v>
+        <v>122692913</v>
       </c>
       <c r="B44" t="n">
         <v>78660</v>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736006</v>
+        <v>736262</v>
       </c>
       <c r="R44" t="n">
-        <v>7413410</v>
+        <v>7413022</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692850</v>
+        <v>122692853</v>
       </c>
       <c r="B45" t="n">
         <v>57384</v>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736028</v>
+        <v>736120</v>
       </c>
       <c r="R45" t="n">
-        <v>7413218</v>
+        <v>7412935</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692896</v>
+        <v>122692851</v>
       </c>
       <c r="B46" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736227</v>
+        <v>736115</v>
       </c>
       <c r="R46" t="n">
-        <v>7413172</v>
+        <v>7412928</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692893</v>
+        <v>122692908</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735982</v>
+        <v>736202</v>
       </c>
       <c r="R3" t="n">
-        <v>7413229</v>
+        <v>7413250</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692905</v>
+        <v>122692893</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736175</v>
+        <v>735982</v>
       </c>
       <c r="R4" t="n">
-        <v>7413127</v>
+        <v>7413229</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692908</v>
+        <v>122692905</v>
       </c>
       <c r="B5" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736202</v>
+        <v>736175</v>
       </c>
       <c r="R5" t="n">
-        <v>7413250</v>
+        <v>7413127</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692867</v>
+        <v>122692879</v>
       </c>
       <c r="B10" t="n">
-        <v>57537</v>
+        <v>78396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,21 +1514,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736165</v>
+        <v>736253</v>
       </c>
       <c r="R10" t="n">
-        <v>7413161</v>
+        <v>7413052</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1582,6 +1582,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692879</v>
+        <v>122692867</v>
       </c>
       <c r="B12" t="n">
-        <v>78396</v>
+        <v>57537</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736253</v>
+        <v>736165</v>
       </c>
       <c r="R12" t="n">
-        <v>7413052</v>
+        <v>7413161</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1787,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692896</v>
+        <v>122692880</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736227</v>
+        <v>736205</v>
       </c>
       <c r="R13" t="n">
-        <v>7413172</v>
+        <v>7412943</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1890,6 +1890,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1908,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692880</v>
+        <v>122692896</v>
       </c>
       <c r="B14" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736205</v>
+        <v>736227</v>
       </c>
       <c r="R14" t="n">
-        <v>7412943</v>
+        <v>7413172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1992,7 +1993,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692892</v>
+        <v>122692850</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2445,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735982</v>
+        <v>736028</v>
       </c>
       <c r="R19" t="n">
-        <v>7413172</v>
+        <v>7413218</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692850</v>
+        <v>122692864</v>
       </c>
       <c r="B20" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736028</v>
+        <v>736292</v>
       </c>
       <c r="R20" t="n">
-        <v>7413218</v>
+        <v>7412983</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692864</v>
+        <v>122692892</v>
       </c>
       <c r="B21" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736292</v>
+        <v>735982</v>
       </c>
       <c r="R21" t="n">
-        <v>7412983</v>
+        <v>7413172</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692886</v>
+        <v>122692862</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,41 +4082,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736116</v>
+        <v>735946</v>
       </c>
       <c r="R35" t="n">
-        <v>7412995</v>
+        <v>7413485</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4151,13 +4148,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4176,7 +4177,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692900</v>
+        <v>122692886</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4210,16 +4211,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736268</v>
+        <v>736116</v>
       </c>
       <c r="R36" t="n">
-        <v>7413074</v>
+        <v>7412995</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4260,6 +4264,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4278,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692862</v>
+        <v>122692900</v>
       </c>
       <c r="B37" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4290,25 +4295,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4318,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735946</v>
+        <v>736268</v>
       </c>
       <c r="R37" t="n">
-        <v>7413485</v>
+        <v>7413074</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4354,11 +4359,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4589,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692916</v>
+        <v>122692866</v>
       </c>
       <c r="B40" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736092</v>
+        <v>736167</v>
       </c>
       <c r="R40" t="n">
-        <v>7413264</v>
+        <v>7413025</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4673,7 +4673,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4692,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692901</v>
+        <v>122692916</v>
       </c>
       <c r="B41" t="n">
         <v>78660</v>
@@ -4732,10 +4731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736256</v>
+        <v>736092</v>
       </c>
       <c r="R41" t="n">
-        <v>7413074</v>
+        <v>7413264</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4776,6 +4775,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692866</v>
+        <v>122692901</v>
       </c>
       <c r="B42" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,21 +4810,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736167</v>
+        <v>736256</v>
       </c>
       <c r="R42" t="n">
-        <v>7413025</v>
+        <v>7413074</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692862</v>
+        <v>122692886</v>
       </c>
       <c r="B35" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,38 +4082,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>735946</v>
+        <v>736116</v>
       </c>
       <c r="R35" t="n">
-        <v>7413485</v>
+        <v>7412995</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4148,17 +4151,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4177,7 +4176,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692886</v>
+        <v>122692900</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4211,19 +4210,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736116</v>
+        <v>736268</v>
       </c>
       <c r="R36" t="n">
-        <v>7412995</v>
+        <v>7413074</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,7 +4260,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4278,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692900</v>
+        <v>122692862</v>
       </c>
       <c r="B37" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4295,25 +4290,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4323,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736268</v>
+        <v>735946</v>
       </c>
       <c r="R37" t="n">
-        <v>7413074</v>
+        <v>7413485</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4359,6 +4354,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692908</v>
+        <v>122692893</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736202</v>
+        <v>735982</v>
       </c>
       <c r="R3" t="n">
-        <v>7413250</v>
+        <v>7413229</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692893</v>
+        <v>122692905</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735982</v>
+        <v>736175</v>
       </c>
       <c r="R4" t="n">
-        <v>7413229</v>
+        <v>7413127</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692905</v>
+        <v>122692908</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736175</v>
+        <v>736202</v>
       </c>
       <c r="R5" t="n">
-        <v>7413127</v>
+        <v>7413250</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692880</v>
+        <v>122692896</v>
       </c>
       <c r="B13" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736205</v>
+        <v>736227</v>
       </c>
       <c r="R13" t="n">
-        <v>7412943</v>
+        <v>7413172</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1890,7 +1890,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692896</v>
+        <v>122692880</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736227</v>
+        <v>736205</v>
       </c>
       <c r="R14" t="n">
-        <v>7413172</v>
+        <v>7412943</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1993,6 +1992,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692896</v>
+        <v>122692880</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736227</v>
+        <v>736205</v>
       </c>
       <c r="R13" t="n">
-        <v>7413172</v>
+        <v>7412943</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1890,6 +1890,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1908,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692880</v>
+        <v>122692896</v>
       </c>
       <c r="B14" t="n">
-        <v>78396</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736205</v>
+        <v>736227</v>
       </c>
       <c r="R14" t="n">
-        <v>7412943</v>
+        <v>7413172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1992,7 +1993,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692866</v>
+        <v>122692916</v>
       </c>
       <c r="B40" t="n">
-        <v>57537</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736167</v>
+        <v>736092</v>
       </c>
       <c r="R40" t="n">
-        <v>7413025</v>
+        <v>7413264</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4673,6 +4673,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,7 +4692,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692916</v>
+        <v>122692901</v>
       </c>
       <c r="B41" t="n">
         <v>78660</v>
@@ -4731,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736092</v>
+        <v>736256</v>
       </c>
       <c r="R41" t="n">
-        <v>7413264</v>
+        <v>7413074</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4775,7 +4776,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692901</v>
+        <v>122692866</v>
       </c>
       <c r="B42" t="n">
-        <v>78660</v>
+        <v>57537</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,21 +4810,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736256</v>
+        <v>736167</v>
       </c>
       <c r="R42" t="n">
-        <v>7413074</v>
+        <v>7413025</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692879</v>
+        <v>122692867</v>
       </c>
       <c r="B10" t="n">
-        <v>78396</v>
+        <v>57537</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,21 +1514,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736253</v>
+        <v>736165</v>
       </c>
       <c r="R10" t="n">
-        <v>7413052</v>
+        <v>7413161</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1582,7 +1582,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1704,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692867</v>
+        <v>122692879</v>
       </c>
       <c r="B12" t="n">
-        <v>57537</v>
+        <v>78396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1719,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736165</v>
+        <v>736253</v>
       </c>
       <c r="R12" t="n">
-        <v>7413161</v>
+        <v>7413052</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1788,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692886</v>
+        <v>122692862</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>56594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4082,41 +4082,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736116</v>
+        <v>735946</v>
       </c>
       <c r="R35" t="n">
-        <v>7412995</v>
+        <v>7413485</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4151,13 +4148,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4176,7 +4177,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692900</v>
+        <v>122692886</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4210,16 +4211,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736268</v>
+        <v>736116</v>
       </c>
       <c r="R36" t="n">
-        <v>7413074</v>
+        <v>7412995</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4260,6 +4264,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4278,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692862</v>
+        <v>122692900</v>
       </c>
       <c r="B37" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4290,25 +4295,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4318,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735946</v>
+        <v>736268</v>
       </c>
       <c r="R37" t="n">
-        <v>7413485</v>
+        <v>7413074</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4354,11 +4359,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5303,6 +5303,1370 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122786874</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>736381</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7413321</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122786872</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>736447</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7413232</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122786919</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>736372</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7413070</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122786923</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>736316</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7413295</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122786888</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>736358</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7413327</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Par</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122786873</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>736260</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7413219</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122786921</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>736417</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7413130</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122786922</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>736463</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7413234</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122786896</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>736223</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7413089</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122786871</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>736468</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7413177</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122786904</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57589</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>736358</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7413327</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122786920</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>736393</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7413048</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122786887</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>736375</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7413284</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692867</v>
+        <v>122692879</v>
       </c>
       <c r="B10" t="n">
-        <v>57537</v>
+        <v>78396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,21 +1514,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736165</v>
+        <v>736253</v>
       </c>
       <c r="R10" t="n">
-        <v>7413161</v>
+        <v>7413052</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1582,6 +1582,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692879</v>
+        <v>122692867</v>
       </c>
       <c r="B12" t="n">
-        <v>78396</v>
+        <v>57537</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736253</v>
+        <v>736165</v>
       </c>
       <c r="R12" t="n">
-        <v>7413052</v>
+        <v>7413161</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1787,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -6667,6 +6667,210 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122800284</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>736110</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7413053</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122800283</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sarkavare, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>736133</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7412935</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1187,7 +1187,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692902</v>
+        <v>122692905</v>
       </c>
       <c r="B7" t="n">
         <v>78762</v>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736287</v>
+        <v>736175</v>
       </c>
       <c r="R7" t="n">
-        <v>7412989</v>
+        <v>7413127</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692905</v>
+        <v>122692902</v>
       </c>
       <c r="B8" t="n">
         <v>78762</v>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736175</v>
+        <v>736287</v>
       </c>
       <c r="R8" t="n">
-        <v>7413127</v>
+        <v>7412989</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692877</v>
+        <v>122692900</v>
       </c>
       <c r="B15" t="n">
-        <v>57627</v>
+        <v>78762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736170</v>
+        <v>736268</v>
       </c>
       <c r="R15" t="n">
-        <v>7413160</v>
+        <v>7413074</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692900</v>
+        <v>122692877</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>57627</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,21 +2123,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736268</v>
+        <v>736170</v>
       </c>
       <c r="R16" t="n">
-        <v>7413074</v>
+        <v>7413160</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692886</v>
+        <v>122692863</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,41 +2430,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736116</v>
+        <v>736167</v>
       </c>
       <c r="R19" t="n">
-        <v>7412995</v>
+        <v>7413243</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2499,13 +2496,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692901</v>
+        <v>122692850</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,21 +2541,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736256</v>
+        <v>736028</v>
       </c>
       <c r="R20" t="n">
-        <v>7413074</v>
+        <v>7413218</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2626,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692863</v>
+        <v>122692886</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>78762</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,38 +2639,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736167</v>
+        <v>736116</v>
       </c>
       <c r="R21" t="n">
-        <v>7413243</v>
+        <v>7412995</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2704,17 +2708,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692850</v>
+        <v>122692901</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736028</v>
+        <v>736256</v>
       </c>
       <c r="R22" t="n">
-        <v>7413218</v>
+        <v>7413074</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692874</v>
+        <v>122692892</v>
       </c>
       <c r="B39" t="n">
-        <v>78499</v>
+        <v>78762</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736203</v>
+        <v>735982</v>
       </c>
       <c r="R39" t="n">
-        <v>7412940</v>
+        <v>7413172</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4569,7 +4569,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4588,7 +4587,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692892</v>
+        <v>122692895</v>
       </c>
       <c r="B40" t="n">
         <v>78762</v>
@@ -4628,10 +4627,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735982</v>
+        <v>736222</v>
       </c>
       <c r="R40" t="n">
-        <v>7413172</v>
+        <v>7413197</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4690,10 +4689,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692895</v>
+        <v>122692874</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>78499</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4706,21 +4705,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4730,10 +4729,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736222</v>
+        <v>736203</v>
       </c>
       <c r="R41" t="n">
-        <v>7413197</v>
+        <v>7412940</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4774,6 +4773,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692880</v>
+        <v>122692915</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736205</v>
+        <v>736095</v>
       </c>
       <c r="R2" t="n">
-        <v>7412943</v>
+        <v>7413383</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692853</v>
+        <v>122692900</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736120</v>
+        <v>736268</v>
       </c>
       <c r="R3" t="n">
-        <v>7412935</v>
+        <v>7413074</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692893</v>
+        <v>122692890</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735982</v>
+        <v>736078</v>
       </c>
       <c r="R4" t="n">
-        <v>7413229</v>
+        <v>7413098</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692887</v>
+        <v>122692879</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735969</v>
+        <v>736253</v>
       </c>
       <c r="R5" t="n">
-        <v>7413433</v>
+        <v>7413052</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692896</v>
+        <v>122692874</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736227</v>
+        <v>736203</v>
       </c>
       <c r="R6" t="n">
-        <v>7413172</v>
+        <v>7412940</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,6 +1169,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1187,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692905</v>
+        <v>122692876</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>57589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1199,25 +1200,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736175</v>
+        <v>736253</v>
       </c>
       <c r="R7" t="n">
-        <v>7413127</v>
+        <v>7413052</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,7 +1293,7 @@
         <v>122692902</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692903</v>
+        <v>122692908</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1403,25 +1404,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736135</v>
+        <v>736202</v>
       </c>
       <c r="R9" t="n">
-        <v>7412970</v>
+        <v>7413250</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1467,6 +1468,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692861</v>
+        <v>122692866</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1505,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1533,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736142</v>
+        <v>736167</v>
       </c>
       <c r="R10" t="n">
-        <v>7413297</v>
+        <v>7413025</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1595,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692889</v>
+        <v>122692886</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,16 +1635,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736006</v>
+        <v>736116</v>
       </c>
       <c r="R11" t="n">
-        <v>7413410</v>
+        <v>7412995</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1698,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692906</v>
+        <v>122692852</v>
       </c>
       <c r="B12" t="n">
-        <v>82549</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1714,21 +1723,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1747,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736295</v>
+        <v>736126</v>
       </c>
       <c r="R12" t="n">
-        <v>7412988</v>
+        <v>7412904</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1782,7 +1791,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1801,7 +1809,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692856</v>
+        <v>122692855</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1841,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736114</v>
+        <v>736124</v>
       </c>
       <c r="R13" t="n">
-        <v>7412934</v>
+        <v>7412945</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1903,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692890</v>
+        <v>122692904</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736078</v>
+        <v>736171</v>
       </c>
       <c r="R14" t="n">
-        <v>7413098</v>
+        <v>7412886</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2005,10 +2013,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692900</v>
+        <v>122692901</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,7 +2053,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736268</v>
+        <v>736256</v>
       </c>
       <c r="R15" t="n">
         <v>7413074</v>
@@ -2107,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692877</v>
+        <v>122692868</v>
       </c>
       <c r="B16" t="n">
-        <v>57627</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,21 +2131,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103022</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,7 +2155,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736170</v>
+        <v>736267</v>
       </c>
       <c r="R16" t="n">
         <v>7413160</v>
@@ -2183,6 +2191,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2209,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692862</v>
+        <v>122692864</v>
       </c>
       <c r="B17" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,25 +2234,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735946</v>
+        <v>736292</v>
       </c>
       <c r="R17" t="n">
-        <v>7413485</v>
+        <v>7412983</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2285,11 +2298,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692855</v>
+        <v>122692906</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2340,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736124</v>
+        <v>736295</v>
       </c>
       <c r="R18" t="n">
-        <v>7412945</v>
+        <v>7412988</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2400,6 +2408,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2418,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692863</v>
+        <v>122692853</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,25 +2439,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736167</v>
+        <v>736120</v>
       </c>
       <c r="R19" t="n">
-        <v>7413243</v>
+        <v>7412935</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2494,11 +2503,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692850</v>
+        <v>122692862</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,25 +2541,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736028</v>
+        <v>735946</v>
       </c>
       <c r="R20" t="n">
-        <v>7413218</v>
+        <v>7413485</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2601,6 +2605,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2627,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692886</v>
+        <v>122692860</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,41 +2648,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736116</v>
+        <v>736132</v>
       </c>
       <c r="R21" t="n">
-        <v>7412995</v>
+        <v>7412974</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,13 +2714,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2733,10 +2743,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692901</v>
+        <v>122692903</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736256</v>
+        <v>736135</v>
       </c>
       <c r="R22" t="n">
-        <v>7413074</v>
+        <v>7412970</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2835,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692866</v>
+        <v>122692861</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2847,25 +2857,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736167</v>
+        <v>736142</v>
       </c>
       <c r="R23" t="n">
-        <v>7413025</v>
+        <v>7413297</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,10 +2947,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692864</v>
+        <v>122692897</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,21 +2963,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736292</v>
+        <v>736248</v>
       </c>
       <c r="R24" t="n">
-        <v>7412983</v>
+        <v>7413169</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3039,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692851</v>
+        <v>122692899</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,21 +3065,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736115</v>
+        <v>736253</v>
       </c>
       <c r="R25" t="n">
-        <v>7412928</v>
+        <v>7413096</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3141,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692879</v>
+        <v>122692863</v>
       </c>
       <c r="B26" t="n">
-        <v>78498</v>
+        <v>56688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3153,25 +3163,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736253</v>
+        <v>736167</v>
       </c>
       <c r="R26" t="n">
-        <v>7413052</v>
+        <v>7413243</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3219,13 +3229,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3244,10 +3258,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692897</v>
+        <v>122692880</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3260,21 +3274,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3284,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736248</v>
+        <v>736205</v>
       </c>
       <c r="R27" t="n">
-        <v>7413169</v>
+        <v>7412943</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3328,6 +3342,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3346,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692867</v>
+        <v>122692893</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3362,21 +3377,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3386,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736165</v>
+        <v>735982</v>
       </c>
       <c r="R28" t="n">
-        <v>7413161</v>
+        <v>7413229</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3448,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692860</v>
+        <v>122692892</v>
       </c>
       <c r="B29" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,25 +3475,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3488,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736132</v>
+        <v>735982</v>
       </c>
       <c r="R29" t="n">
-        <v>7412974</v>
+        <v>7413172</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3524,11 +3539,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,10 +3565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692904</v>
+        <v>122692916</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3595,10 +3605,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736171</v>
+        <v>736092</v>
       </c>
       <c r="R30" t="n">
-        <v>7412886</v>
+        <v>7413264</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3639,6 +3649,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3657,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692852</v>
+        <v>122692867</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,21 +3684,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736126</v>
+        <v>736165</v>
       </c>
       <c r="R31" t="n">
-        <v>7412904</v>
+        <v>7413161</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3759,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692891</v>
+        <v>122692887</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3799,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736029</v>
+        <v>735969</v>
       </c>
       <c r="R32" t="n">
-        <v>7413135</v>
+        <v>7413433</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3843,6 +3854,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3861,10 +3873,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692913</v>
+        <v>122692905</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3901,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736262</v>
+        <v>736175</v>
       </c>
       <c r="R33" t="n">
-        <v>7413022</v>
+        <v>7413127</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3945,7 +3957,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3964,10 +3975,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692868</v>
+        <v>122692891</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,21 +3991,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736267</v>
+        <v>736029</v>
       </c>
       <c r="R34" t="n">
-        <v>7413160</v>
+        <v>7413135</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4040,11 +4051,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,10 +4077,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692865</v>
+        <v>122692888</v>
       </c>
       <c r="B35" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736116</v>
+        <v>736141</v>
       </c>
       <c r="R35" t="n">
-        <v>7412997</v>
+        <v>7413344</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4155,6 +4161,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4173,10 +4180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692916</v>
+        <v>122692913</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4213,10 +4220,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736092</v>
+        <v>736262</v>
       </c>
       <c r="R36" t="n">
-        <v>7413264</v>
+        <v>7413022</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4276,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692908</v>
+        <v>122692896</v>
       </c>
       <c r="B37" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4288,25 +4295,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4316,10 +4323,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736202</v>
+        <v>736227</v>
       </c>
       <c r="R37" t="n">
-        <v>7413250</v>
+        <v>7413172</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4352,11 +4359,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4383,10 +4385,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692899</v>
+        <v>122692865</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4399,21 +4401,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4423,10 +4425,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736253</v>
+        <v>736116</v>
       </c>
       <c r="R38" t="n">
-        <v>7413096</v>
+        <v>7412997</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4485,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692892</v>
+        <v>122692859</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4497,25 +4499,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4525,10 +4527,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>735982</v>
+        <v>736141</v>
       </c>
       <c r="R39" t="n">
-        <v>7413172</v>
+        <v>7413297</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4587,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692895</v>
+        <v>122692856</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4603,21 +4605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4627,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736222</v>
+        <v>736114</v>
       </c>
       <c r="R40" t="n">
-        <v>7413197</v>
+        <v>7412934</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4689,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692874</v>
+        <v>122692877</v>
       </c>
       <c r="B41" t="n">
-        <v>78499</v>
+        <v>57627</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,21 +4707,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>103022</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4729,10 +4731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736203</v>
+        <v>736170</v>
       </c>
       <c r="R41" t="n">
-        <v>7412940</v>
+        <v>7413160</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4773,7 +4775,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4793,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692859</v>
+        <v>122692914</v>
       </c>
       <c r="B42" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4804,25 +4805,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,7 +4836,7 @@
         <v>736141</v>
       </c>
       <c r="R42" t="n">
-        <v>7413297</v>
+        <v>7413319</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4876,6 +4877,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4894,10 +4896,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692914</v>
+        <v>122692889</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4934,10 +4936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736141</v>
+        <v>736006</v>
       </c>
       <c r="R43" t="n">
-        <v>7413319</v>
+        <v>7413410</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4997,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692915</v>
+        <v>122692895</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5037,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736095</v>
+        <v>736222</v>
       </c>
       <c r="R44" t="n">
-        <v>7413383</v>
+        <v>7413197</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5081,7 +5083,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5100,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692888</v>
+        <v>122692851</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5116,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5140,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736141</v>
+        <v>736115</v>
       </c>
       <c r="R45" t="n">
-        <v>7413344</v>
+        <v>7412928</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5184,7 +5185,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692876</v>
+        <v>122692850</v>
       </c>
       <c r="B46" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5215,20 +5215,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736253</v>
+        <v>736028</v>
       </c>
       <c r="R46" t="n">
-        <v>7413052</v>
+        <v>7413218</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786896</v>
+        <v>122786920</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736223</v>
+        <v>736393</v>
       </c>
       <c r="R47" t="n">
-        <v>7413089</v>
+        <v>7413048</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786922</v>
+        <v>122786887</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5419,38 +5419,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736463</v>
+        <v>736375</v>
       </c>
       <c r="R48" t="n">
-        <v>7413234</v>
+        <v>7413284</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5483,6 +5487,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5509,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786872</v>
+        <v>122786921</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,21 +5534,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5558,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736447</v>
+        <v>736417</v>
       </c>
       <c r="R49" t="n">
-        <v>7413232</v>
+        <v>7413130</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5585,11 +5594,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5616,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786888</v>
+        <v>122786871</v>
       </c>
       <c r="B50" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,38 +5636,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736358</v>
+        <v>736468</v>
       </c>
       <c r="R50" t="n">
-        <v>7413327</v>
+        <v>7413177</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5727,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786904</v>
+        <v>122786896</v>
       </c>
       <c r="B51" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,20 +5739,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736358</v>
+        <v>736223</v>
       </c>
       <c r="R51" t="n">
-        <v>7413327</v>
+        <v>7413089</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5829,10 +5829,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786923</v>
+        <v>122786873</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736316</v>
+        <v>736260</v>
       </c>
       <c r="R52" t="n">
-        <v>7413295</v>
+        <v>7413219</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5905,6 +5905,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5931,10 +5936,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786887</v>
+        <v>122786872</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,42 +5948,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736375</v>
+        <v>736447</v>
       </c>
       <c r="R53" t="n">
-        <v>7413284</v>
+        <v>7413232</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6015,7 +6016,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6042,10 +6043,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786920</v>
+        <v>122786919</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6082,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736393</v>
+        <v>736372</v>
       </c>
       <c r="R54" t="n">
-        <v>7413048</v>
+        <v>7413070</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6144,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786873</v>
+        <v>122786904</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6156,20 +6157,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6184,10 +6185,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736260</v>
+        <v>736358</v>
       </c>
       <c r="R55" t="n">
-        <v>7413219</v>
+        <v>7413327</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6220,11 +6221,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6251,7 +6247,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786871</v>
+        <v>122786874</v>
       </c>
       <c r="B56" t="n">
         <v>57478</v>
@@ -6291,10 +6287,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736468</v>
+        <v>736381</v>
       </c>
       <c r="R56" t="n">
-        <v>7413177</v>
+        <v>7413321</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6331,7 +6327,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Över 20 ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6358,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786919</v>
+        <v>122786888</v>
       </c>
       <c r="B57" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6374,34 +6370,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736372</v>
+        <v>736358</v>
       </c>
       <c r="R57" t="n">
-        <v>7413070</v>
+        <v>7413327</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6434,6 +6434,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6460,10 +6465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786921</v>
+        <v>122786923</v>
       </c>
       <c r="B58" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6500,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736417</v>
+        <v>736316</v>
       </c>
       <c r="R58" t="n">
-        <v>7413130</v>
+        <v>7413295</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6562,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786874</v>
+        <v>122786922</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6578,21 +6583,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6602,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736381</v>
+        <v>736463</v>
       </c>
       <c r="R59" t="n">
-        <v>7413321</v>
+        <v>7413234</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6638,11 +6643,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R60" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R61" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692902</v>
+        <v>122692866</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736287</v>
+        <v>736167</v>
       </c>
       <c r="R8" t="n">
-        <v>7412989</v>
+        <v>7413025</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692908</v>
+        <v>122692902</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1404,25 +1404,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736202</v>
+        <v>736287</v>
       </c>
       <c r="R9" t="n">
-        <v>7413250</v>
+        <v>7412989</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1468,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692866</v>
+        <v>122692908</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,25 +1506,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736167</v>
+        <v>736202</v>
       </c>
       <c r="R10" t="n">
-        <v>7413025</v>
+        <v>7413250</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1575,6 +1570,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692855</v>
+        <v>122692868</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,16 +1825,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736124</v>
+        <v>736267</v>
       </c>
       <c r="R13" t="n">
-        <v>7412945</v>
+        <v>7413160</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,6 +1885,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1911,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692904</v>
+        <v>122692855</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736171</v>
+        <v>736124</v>
       </c>
       <c r="R14" t="n">
-        <v>7412886</v>
+        <v>7412945</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2013,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692901</v>
+        <v>122692864</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,21 +2034,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2053,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736256</v>
+        <v>736292</v>
       </c>
       <c r="R15" t="n">
-        <v>7413074</v>
+        <v>7412983</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2115,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692868</v>
+        <v>122692904</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,21 +2136,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736267</v>
+        <v>736171</v>
       </c>
       <c r="R16" t="n">
-        <v>7413160</v>
+        <v>7412886</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2191,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692864</v>
+        <v>122692901</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736292</v>
+        <v>736256</v>
       </c>
       <c r="R17" t="n">
-        <v>7412983</v>
+        <v>7413074</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -3258,10 +3258,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692880</v>
+        <v>122692893</v>
       </c>
       <c r="B27" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3274,21 +3274,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736205</v>
+        <v>735982</v>
       </c>
       <c r="R27" t="n">
-        <v>7412943</v>
+        <v>7413229</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3342,7 +3342,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3361,7 +3360,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692893</v>
+        <v>122692892</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3404,7 +3403,7 @@
         <v>735982</v>
       </c>
       <c r="R28" t="n">
-        <v>7413229</v>
+        <v>7413172</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3463,7 +3462,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692892</v>
+        <v>122692916</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3503,10 +3502,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735982</v>
+        <v>736092</v>
       </c>
       <c r="R29" t="n">
-        <v>7413172</v>
+        <v>7413264</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,6 +3546,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692916</v>
+        <v>122692880</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,21 +3581,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736092</v>
+        <v>736205</v>
       </c>
       <c r="R30" t="n">
-        <v>7413264</v>
+        <v>7412943</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4589,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692856</v>
+        <v>122692877</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57627</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736114</v>
+        <v>736170</v>
       </c>
       <c r="R40" t="n">
-        <v>7412934</v>
+        <v>7413160</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692877</v>
+        <v>122692856</v>
       </c>
       <c r="B41" t="n">
-        <v>57627</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736170</v>
+        <v>736114</v>
       </c>
       <c r="R41" t="n">
-        <v>7413160</v>
+        <v>7412934</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -6354,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786888</v>
+        <v>122786923</v>
       </c>
       <c r="B57" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6370,38 +6370,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736358</v>
+        <v>736316</v>
       </c>
       <c r="R57" t="n">
-        <v>7413327</v>
+        <v>7413295</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6434,11 +6430,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6465,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786923</v>
+        <v>122786888</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6481,34 +6472,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736316</v>
+        <v>736358</v>
       </c>
       <c r="R58" t="n">
-        <v>7413295</v>
+        <v>7413327</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6541,6 +6536,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692915</v>
+        <v>122692887</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736095</v>
+        <v>735969</v>
       </c>
       <c r="R2" t="n">
-        <v>7413383</v>
+        <v>7413433</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692900</v>
+        <v>122692890</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736268</v>
+        <v>736078</v>
       </c>
       <c r="R3" t="n">
-        <v>7413074</v>
+        <v>7413098</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692890</v>
+        <v>122692906</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736078</v>
+        <v>736295</v>
       </c>
       <c r="R4" t="n">
-        <v>7413098</v>
+        <v>7412988</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,6 +964,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692879</v>
+        <v>122692874</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736253</v>
+        <v>736203</v>
       </c>
       <c r="R5" t="n">
-        <v>7413052</v>
+        <v>7412940</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,10 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692874</v>
+        <v>122692901</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736203</v>
+        <v>736256</v>
       </c>
       <c r="R6" t="n">
-        <v>7412940</v>
+        <v>7413074</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,7 +1170,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692876</v>
+        <v>122692852</v>
       </c>
       <c r="B7" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1200,20 +1200,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736253</v>
+        <v>736126</v>
       </c>
       <c r="R7" t="n">
-        <v>7413052</v>
+        <v>7412904</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692866</v>
+        <v>122692851</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736167</v>
+        <v>736115</v>
       </c>
       <c r="R8" t="n">
-        <v>7413025</v>
+        <v>7412928</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692902</v>
+        <v>122692876</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1404,25 +1404,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736287</v>
+        <v>736253</v>
       </c>
       <c r="R9" t="n">
-        <v>7412989</v>
+        <v>7413052</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692908</v>
+        <v>122692862</v>
       </c>
       <c r="B10" t="n">
         <v>56688</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736202</v>
+        <v>735946</v>
       </c>
       <c r="R10" t="n">
-        <v>7413250</v>
+        <v>7413485</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692886</v>
+        <v>122692879</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,37 +1617,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736116</v>
+        <v>736253</v>
       </c>
       <c r="R11" t="n">
-        <v>7412995</v>
+        <v>7413052</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1707,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692852</v>
+        <v>122692865</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1747,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736126</v>
+        <v>736116</v>
       </c>
       <c r="R12" t="n">
-        <v>7412904</v>
+        <v>7412997</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1809,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692868</v>
+        <v>122692856</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,16 +1822,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1849,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736267</v>
+        <v>736114</v>
       </c>
       <c r="R13" t="n">
-        <v>7413160</v>
+        <v>7412934</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,11 +1882,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1916,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692855</v>
+        <v>122692897</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736124</v>
+        <v>736248</v>
       </c>
       <c r="R14" t="n">
-        <v>7412945</v>
+        <v>7413169</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692864</v>
+        <v>122692886</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2034,34 +2026,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736292</v>
+        <v>736116</v>
       </c>
       <c r="R15" t="n">
-        <v>7412983</v>
+        <v>7412995</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2102,6 +2097,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2120,10 +2116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692904</v>
+        <v>122692855</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736171</v>
+        <v>736124</v>
       </c>
       <c r="R16" t="n">
-        <v>7412886</v>
+        <v>7412945</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2222,7 +2218,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692901</v>
+        <v>122692888</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2262,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736256</v>
+        <v>736141</v>
       </c>
       <c r="R17" t="n">
-        <v>7413074</v>
+        <v>7413344</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2306,6 +2302,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2324,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692906</v>
+        <v>122692850</v>
       </c>
       <c r="B18" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736295</v>
+        <v>736028</v>
       </c>
       <c r="R18" t="n">
-        <v>7412988</v>
+        <v>7413218</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2408,7 +2405,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692853</v>
+        <v>122692905</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736120</v>
+        <v>736175</v>
       </c>
       <c r="R19" t="n">
-        <v>7412935</v>
+        <v>7413127</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692862</v>
+        <v>122692900</v>
       </c>
       <c r="B20" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735946</v>
+        <v>736268</v>
       </c>
       <c r="R20" t="n">
-        <v>7413485</v>
+        <v>7413074</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2605,11 +2601,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,7 +2734,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692903</v>
+        <v>122692893</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736135</v>
+        <v>735982</v>
       </c>
       <c r="R22" t="n">
-        <v>7412970</v>
+        <v>7413229</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2845,10 +2836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692861</v>
+        <v>122692916</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,25 +2848,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2885,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736142</v>
+        <v>736092</v>
       </c>
       <c r="R23" t="n">
-        <v>7413297</v>
+        <v>7413264</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,6 +2920,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2947,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692897</v>
+        <v>122692859</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736248</v>
+        <v>736141</v>
       </c>
       <c r="R24" t="n">
-        <v>7413169</v>
+        <v>7413297</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3049,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692899</v>
+        <v>122692896</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3089,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736253</v>
+        <v>736227</v>
       </c>
       <c r="R25" t="n">
-        <v>7413096</v>
+        <v>7413172</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3151,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692863</v>
+        <v>122692891</v>
       </c>
       <c r="B26" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736167</v>
+        <v>736029</v>
       </c>
       <c r="R26" t="n">
-        <v>7413243</v>
+        <v>7413135</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3227,11 +3219,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3258,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692893</v>
+        <v>122692868</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3274,21 +3261,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735982</v>
+        <v>736267</v>
       </c>
       <c r="R27" t="n">
-        <v>7413229</v>
+        <v>7413160</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3334,6 +3321,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3360,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692892</v>
+        <v>122692899</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3400,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735982</v>
+        <v>736253</v>
       </c>
       <c r="R28" t="n">
-        <v>7413172</v>
+        <v>7413096</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3462,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692916</v>
+        <v>122692892</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3502,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736092</v>
+        <v>735982</v>
       </c>
       <c r="R29" t="n">
-        <v>7413264</v>
+        <v>7413172</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3546,7 +3538,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3565,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692880</v>
+        <v>122692877</v>
       </c>
       <c r="B30" t="n">
-        <v>78502</v>
+        <v>57627</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,21 +3572,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>103022</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3605,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736205</v>
+        <v>736170</v>
       </c>
       <c r="R30" t="n">
-        <v>7412943</v>
+        <v>7413160</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,7 +3640,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3668,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692867</v>
+        <v>122692913</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3684,21 +3674,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3708,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736165</v>
+        <v>736262</v>
       </c>
       <c r="R31" t="n">
-        <v>7413161</v>
+        <v>7413022</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3752,6 +3742,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3770,10 +3761,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692887</v>
+        <v>122692863</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3782,25 +3773,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3810,10 +3801,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735969</v>
+        <v>736167</v>
       </c>
       <c r="R32" t="n">
-        <v>7413433</v>
+        <v>7413243</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3848,13 +3839,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3873,7 +3868,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692905</v>
+        <v>122692914</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3913,10 +3908,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736175</v>
+        <v>736141</v>
       </c>
       <c r="R33" t="n">
-        <v>7413127</v>
+        <v>7413319</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3957,6 +3952,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3975,10 +3971,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692891</v>
+        <v>122692867</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,21 +3987,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4011,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736029</v>
+        <v>736165</v>
       </c>
       <c r="R34" t="n">
-        <v>7413135</v>
+        <v>7413161</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4077,7 +4073,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692888</v>
+        <v>122692889</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4117,10 +4113,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736141</v>
+        <v>736006</v>
       </c>
       <c r="R35" t="n">
-        <v>7413344</v>
+        <v>7413410</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4180,7 +4176,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692913</v>
+        <v>122692902</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4220,10 +4216,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736262</v>
+        <v>736287</v>
       </c>
       <c r="R36" t="n">
-        <v>7413022</v>
+        <v>7412989</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4264,7 +4260,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4283,7 +4278,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692896</v>
+        <v>122692903</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4323,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736227</v>
+        <v>736135</v>
       </c>
       <c r="R37" t="n">
-        <v>7413172</v>
+        <v>7412970</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4385,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692865</v>
+        <v>122692853</v>
       </c>
       <c r="B38" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4401,21 +4396,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4425,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736116</v>
+        <v>736120</v>
       </c>
       <c r="R38" t="n">
-        <v>7412997</v>
+        <v>7412935</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4487,7 +4482,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692859</v>
+        <v>122692908</v>
       </c>
       <c r="B39" t="n">
         <v>56688</v>
@@ -4527,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736141</v>
+        <v>736202</v>
       </c>
       <c r="R39" t="n">
-        <v>7413297</v>
+        <v>7413250</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4563,6 +4558,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4589,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692877</v>
+        <v>122692880</v>
       </c>
       <c r="B40" t="n">
-        <v>57627</v>
+        <v>78502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4605,21 +4605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103022</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736170</v>
+        <v>736205</v>
       </c>
       <c r="R40" t="n">
-        <v>7413160</v>
+        <v>7412943</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4673,6 +4673,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692856</v>
+        <v>122692895</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4707,21 +4708,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4731,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736114</v>
+        <v>736222</v>
       </c>
       <c r="R41" t="n">
-        <v>7412934</v>
+        <v>7413197</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4793,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692914</v>
+        <v>122692861</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4805,25 +4806,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4833,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736141</v>
+        <v>736142</v>
       </c>
       <c r="R42" t="n">
-        <v>7413319</v>
+        <v>7413297</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4877,7 +4878,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692889</v>
+        <v>122692915</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736006</v>
+        <v>736095</v>
       </c>
       <c r="R43" t="n">
-        <v>7413410</v>
+        <v>7413383</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692895</v>
+        <v>122692866</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736222</v>
+        <v>736167</v>
       </c>
       <c r="R44" t="n">
-        <v>7413197</v>
+        <v>7413025</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5101,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692851</v>
+        <v>122692904</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736115</v>
+        <v>736171</v>
       </c>
       <c r="R45" t="n">
-        <v>7412928</v>
+        <v>7412886</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692850</v>
+        <v>122692864</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736028</v>
+        <v>736292</v>
       </c>
       <c r="R46" t="n">
-        <v>7413218</v>
+        <v>7412983</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786920</v>
+        <v>122786923</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736393</v>
+        <v>736316</v>
       </c>
       <c r="R47" t="n">
-        <v>7413048</v>
+        <v>7413295</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786887</v>
+        <v>122786904</v>
       </c>
       <c r="B48" t="n">
-        <v>56688</v>
+        <v>57589</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,38 +5423,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736375</v>
+        <v>736358</v>
       </c>
       <c r="R48" t="n">
-        <v>7413284</v>
+        <v>7413327</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5487,11 +5483,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5518,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786921</v>
+        <v>122786871</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5534,21 +5525,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5558,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736417</v>
+        <v>736468</v>
       </c>
       <c r="R49" t="n">
-        <v>7413130</v>
+        <v>7413177</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5594,6 +5585,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5620,7 +5616,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786871</v>
+        <v>122786874</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -5660,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736468</v>
+        <v>736381</v>
       </c>
       <c r="R50" t="n">
-        <v>7413177</v>
+        <v>7413321</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5700,7 +5696,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Över 20 ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5727,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786896</v>
+        <v>122786873</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,16 +5739,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5767,10 +5763,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736223</v>
+        <v>736260</v>
       </c>
       <c r="R51" t="n">
-        <v>7413089</v>
+        <v>7413219</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5803,6 +5799,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5829,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786873</v>
+        <v>122786922</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,21 +5846,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5869,10 +5870,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736260</v>
+        <v>736463</v>
       </c>
       <c r="R52" t="n">
-        <v>7413219</v>
+        <v>7413234</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5905,11 +5906,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5936,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786872</v>
+        <v>122786921</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5952,21 +5948,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5976,10 +5972,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736447</v>
+        <v>736417</v>
       </c>
       <c r="R53" t="n">
-        <v>7413232</v>
+        <v>7413130</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6012,11 +6008,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6043,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786919</v>
+        <v>122786872</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6059,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6083,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736372</v>
+        <v>736447</v>
       </c>
       <c r="R54" t="n">
-        <v>7413070</v>
+        <v>7413232</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6119,6 +6110,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786904</v>
+        <v>122786919</v>
       </c>
       <c r="B55" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,25 +6153,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6185,10 +6181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736358</v>
+        <v>736372</v>
       </c>
       <c r="R55" t="n">
-        <v>7413327</v>
+        <v>7413070</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6247,10 +6243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786874</v>
+        <v>122786888</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6263,34 +6259,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736381</v>
+        <v>736358</v>
       </c>
       <c r="R56" t="n">
-        <v>7413321</v>
+        <v>7413327</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786923</v>
+        <v>122786887</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6366,38 +6366,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736316</v>
+        <v>736375</v>
       </c>
       <c r="R57" t="n">
-        <v>7413295</v>
+        <v>7413284</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6430,6 +6434,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6456,10 +6465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786888</v>
+        <v>122786896</v>
       </c>
       <c r="B58" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,38 +6481,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736358</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>7413327</v>
+        <v>7413089</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6536,11 +6541,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6567,7 +6567,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786922</v>
+        <v>122786920</v>
       </c>
       <c r="B59" t="n">
         <v>78766</v>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736463</v>
+        <v>736393</v>
       </c>
       <c r="R59" t="n">
-        <v>7413234</v>
+        <v>7413048</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R60" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R61" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692887</v>
+        <v>122692863</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735969</v>
+        <v>736167</v>
       </c>
       <c r="R2" t="n">
-        <v>7413433</v>
+        <v>7413243</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,13 +753,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692890</v>
+        <v>122692906</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736078</v>
+        <v>736295</v>
       </c>
       <c r="R3" t="n">
-        <v>7413098</v>
+        <v>7412988</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692906</v>
+        <v>122692896</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736295</v>
+        <v>736227</v>
       </c>
       <c r="R4" t="n">
-        <v>7412988</v>
+        <v>7413172</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +969,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692874</v>
+        <v>122692877</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
+        <v>57627</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>103022</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736203</v>
+        <v>736170</v>
       </c>
       <c r="R5" t="n">
-        <v>7412940</v>
+        <v>7413160</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1067,7 +1071,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1086,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692901</v>
+        <v>122692905</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1126,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736256</v>
+        <v>736175</v>
       </c>
       <c r="R6" t="n">
-        <v>7413074</v>
+        <v>7413127</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1188,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692852</v>
+        <v>122692913</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1204,21 +1207,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736126</v>
+        <v>736262</v>
       </c>
       <c r="R7" t="n">
-        <v>7412904</v>
+        <v>7413022</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1272,6 +1275,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692851</v>
+        <v>122692887</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1306,21 +1310,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736115</v>
+        <v>735969</v>
       </c>
       <c r="R8" t="n">
-        <v>7412928</v>
+        <v>7413433</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1374,6 +1378,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692876</v>
+        <v>122692892</v>
       </c>
       <c r="B9" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1404,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736253</v>
+        <v>735982</v>
       </c>
       <c r="R9" t="n">
-        <v>7413052</v>
+        <v>7413172</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692862</v>
+        <v>122692879</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1506,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735946</v>
+        <v>736253</v>
       </c>
       <c r="R10" t="n">
-        <v>7413485</v>
+        <v>7413052</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1572,17 +1577,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692879</v>
+        <v>122692888</v>
       </c>
       <c r="B11" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1617,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736253</v>
+        <v>736141</v>
       </c>
       <c r="R11" t="n">
-        <v>7413052</v>
+        <v>7413344</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692865</v>
+        <v>122692868</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736116</v>
+        <v>736267</v>
       </c>
       <c r="R12" t="n">
-        <v>7412997</v>
+        <v>7413160</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1780,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692856</v>
+        <v>122692893</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736114</v>
+        <v>735982</v>
       </c>
       <c r="R13" t="n">
-        <v>7412934</v>
+        <v>7413229</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692897</v>
+        <v>122692901</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1948,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736248</v>
+        <v>736256</v>
       </c>
       <c r="R14" t="n">
-        <v>7413169</v>
+        <v>7413074</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692886</v>
+        <v>122692880</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,37 +2032,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736116</v>
+        <v>736205</v>
       </c>
       <c r="R15" t="n">
-        <v>7412995</v>
+        <v>7412943</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2116,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692855</v>
+        <v>122692861</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,25 +2131,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736124</v>
+        <v>736142</v>
       </c>
       <c r="R16" t="n">
-        <v>7412945</v>
+        <v>7413297</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2218,7 +2221,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692888</v>
+        <v>122692890</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2258,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736141</v>
+        <v>736078</v>
       </c>
       <c r="R17" t="n">
-        <v>7413344</v>
+        <v>7413098</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2302,7 +2305,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2321,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692850</v>
+        <v>122692889</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736028</v>
+        <v>736006</v>
       </c>
       <c r="R18" t="n">
-        <v>7413218</v>
+        <v>7413410</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,6 +2407,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2423,7 +2426,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692905</v>
+        <v>122692902</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2463,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736175</v>
+        <v>736287</v>
       </c>
       <c r="R19" t="n">
-        <v>7413127</v>
+        <v>7412989</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2627,10 +2630,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692860</v>
+        <v>122692904</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,25 +2642,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,10 +2670,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736132</v>
+        <v>736171</v>
       </c>
       <c r="R21" t="n">
-        <v>7412974</v>
+        <v>7412886</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2703,11 +2706,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,10 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692893</v>
+        <v>122692852</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,21 +2748,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2774,10 +2772,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735982</v>
+        <v>736126</v>
       </c>
       <c r="R22" t="n">
-        <v>7413229</v>
+        <v>7412904</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2836,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692916</v>
+        <v>122692862</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,25 +2846,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2876,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736092</v>
+        <v>735946</v>
       </c>
       <c r="R23" t="n">
-        <v>7413264</v>
+        <v>7413485</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2914,13 +2912,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2939,10 +2941,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692859</v>
+        <v>122692897</v>
       </c>
       <c r="B24" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2953,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736141</v>
+        <v>736248</v>
       </c>
       <c r="R24" t="n">
-        <v>7413297</v>
+        <v>7413169</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3041,10 +3043,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692896</v>
+        <v>122692908</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,25 +3055,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3083,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736227</v>
+        <v>736202</v>
       </c>
       <c r="R25" t="n">
-        <v>7413172</v>
+        <v>7413250</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3117,6 +3119,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3143,7 +3150,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692891</v>
+        <v>122692914</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3183,10 +3190,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736029</v>
+        <v>736141</v>
       </c>
       <c r="R26" t="n">
-        <v>7413135</v>
+        <v>7413319</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3227,6 +3234,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3245,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692868</v>
+        <v>122692916</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,21 +3269,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736267</v>
+        <v>736092</v>
       </c>
       <c r="R27" t="n">
-        <v>7413160</v>
+        <v>7413264</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3323,17 +3331,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692899</v>
+        <v>122692855</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,21 +3372,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736253</v>
+        <v>736124</v>
       </c>
       <c r="R28" t="n">
-        <v>7413096</v>
+        <v>7412945</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3454,7 +3458,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692892</v>
+        <v>122692886</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3488,16 +3492,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735982</v>
+        <v>736116</v>
       </c>
       <c r="R29" t="n">
-        <v>7413172</v>
+        <v>7412995</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3538,6 +3545,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3556,10 +3564,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692877</v>
+        <v>122692851</v>
       </c>
       <c r="B30" t="n">
-        <v>57627</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3580,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103022</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3604,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736170</v>
+        <v>736115</v>
       </c>
       <c r="R30" t="n">
-        <v>7413160</v>
+        <v>7412928</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3658,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692913</v>
+        <v>122692866</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,21 +3682,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3706,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736262</v>
+        <v>736167</v>
       </c>
       <c r="R31" t="n">
-        <v>7413022</v>
+        <v>7413025</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3742,7 +3750,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3768,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692863</v>
+        <v>122692874</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3773,25 +3780,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736167</v>
+        <v>736203</v>
       </c>
       <c r="R32" t="n">
-        <v>7413243</v>
+        <v>7412940</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3839,17 +3846,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3868,7 +3871,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692914</v>
+        <v>122692899</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3908,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736141</v>
+        <v>736253</v>
       </c>
       <c r="R33" t="n">
-        <v>7413319</v>
+        <v>7413096</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3952,7 +3955,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3971,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692867</v>
+        <v>122692853</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3987,21 +3989,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4011,10 +4013,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736165</v>
+        <v>736120</v>
       </c>
       <c r="R34" t="n">
-        <v>7413161</v>
+        <v>7412935</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4073,10 +4075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692889</v>
+        <v>122692876</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4085,25 +4087,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4113,10 +4115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736006</v>
+        <v>736253</v>
       </c>
       <c r="R35" t="n">
-        <v>7413410</v>
+        <v>7413052</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4157,7 +4159,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4176,10 +4177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692902</v>
+        <v>122692867</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4192,21 +4193,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4216,10 +4217,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736287</v>
+        <v>736165</v>
       </c>
       <c r="R36" t="n">
-        <v>7412989</v>
+        <v>7413161</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4278,7 +4279,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692903</v>
+        <v>122692915</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4318,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736135</v>
+        <v>736095</v>
       </c>
       <c r="R37" t="n">
-        <v>7412970</v>
+        <v>7413383</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4362,6 +4363,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4380,10 +4382,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692853</v>
+        <v>122692903</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4396,21 +4398,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4422,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736120</v>
+        <v>736135</v>
       </c>
       <c r="R38" t="n">
-        <v>7412935</v>
+        <v>7412970</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4482,10 +4484,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692908</v>
+        <v>122692850</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,25 +4496,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4522,10 +4524,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736202</v>
+        <v>736028</v>
       </c>
       <c r="R39" t="n">
-        <v>7413250</v>
+        <v>7413218</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4558,11 +4560,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4589,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692880</v>
+        <v>122692856</v>
       </c>
       <c r="B40" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4605,21 +4602,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4629,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736205</v>
+        <v>736114</v>
       </c>
       <c r="R40" t="n">
-        <v>7412943</v>
+        <v>7412934</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4673,7 +4670,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4688,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692895</v>
+        <v>122692859</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4704,25 +4700,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4732,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736222</v>
+        <v>736141</v>
       </c>
       <c r="R41" t="n">
-        <v>7413197</v>
+        <v>7413297</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4794,7 +4790,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692861</v>
+        <v>122692860</v>
       </c>
       <c r="B42" t="n">
         <v>56688</v>
@@ -4834,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736142</v>
+        <v>736132</v>
       </c>
       <c r="R42" t="n">
-        <v>7413297</v>
+        <v>7412974</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4870,6 +4866,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4896,10 +4897,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692915</v>
+        <v>122692865</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,21 +4913,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4936,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736095</v>
+        <v>736116</v>
       </c>
       <c r="R43" t="n">
-        <v>7413383</v>
+        <v>7412997</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4980,7 +4981,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4999,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692866</v>
+        <v>122692864</v>
       </c>
       <c r="B44" t="n">
         <v>57631</v>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736167</v>
+        <v>736292</v>
       </c>
       <c r="R44" t="n">
-        <v>7413025</v>
+        <v>7412983</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692904</v>
+        <v>122692891</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736171</v>
+        <v>736029</v>
       </c>
       <c r="R45" t="n">
-        <v>7412886</v>
+        <v>7413135</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692864</v>
+        <v>122692895</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736292</v>
+        <v>736222</v>
       </c>
       <c r="R46" t="n">
-        <v>7412983</v>
+        <v>7413197</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5305,7 +5305,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786923</v>
+        <v>122786920</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736316</v>
+        <v>736393</v>
       </c>
       <c r="R47" t="n">
-        <v>7413295</v>
+        <v>7413048</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786904</v>
+        <v>122786874</v>
       </c>
       <c r="B48" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5419,20 +5419,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736358</v>
+        <v>736381</v>
       </c>
       <c r="R48" t="n">
-        <v>7413327</v>
+        <v>7413321</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5483,6 +5483,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5509,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786871</v>
+        <v>122786922</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,21 +5530,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5549,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736468</v>
+        <v>736463</v>
       </c>
       <c r="R49" t="n">
-        <v>7413177</v>
+        <v>7413234</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5585,11 +5590,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5616,10 +5616,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786874</v>
+        <v>122786921</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736381</v>
+        <v>736417</v>
       </c>
       <c r="R50" t="n">
-        <v>7413321</v>
+        <v>7413130</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5692,11 +5692,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786922</v>
+        <v>122786904</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5842,25 +5837,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5870,10 +5865,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736463</v>
+        <v>736358</v>
       </c>
       <c r="R52" t="n">
-        <v>7413234</v>
+        <v>7413327</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5932,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786921</v>
+        <v>122786872</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,21 +5943,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5972,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736417</v>
+        <v>736447</v>
       </c>
       <c r="R53" t="n">
-        <v>7413130</v>
+        <v>7413232</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6008,6 +6003,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6034,7 +6034,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786872</v>
+        <v>122786871</v>
       </c>
       <c r="B54" t="n">
         <v>57478</v>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736447</v>
+        <v>736468</v>
       </c>
       <c r="R54" t="n">
-        <v>7413232</v>
+        <v>7413177</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6141,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786919</v>
+        <v>122786888</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,34 +6157,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736372</v>
+        <v>736358</v>
       </c>
       <c r="R55" t="n">
-        <v>7413070</v>
+        <v>7413327</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6217,6 +6221,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6243,10 +6252,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786888</v>
+        <v>122786923</v>
       </c>
       <c r="B56" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6259,38 +6268,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736358</v>
+        <v>736316</v>
       </c>
       <c r="R56" t="n">
-        <v>7413327</v>
+        <v>7413295</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6323,11 +6328,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786887</v>
+        <v>122786896</v>
       </c>
       <c r="B57" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6366,42 +6366,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736375</v>
+        <v>736223</v>
       </c>
       <c r="R57" t="n">
-        <v>7413284</v>
+        <v>7413089</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6434,11 +6430,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6465,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786896</v>
+        <v>122786919</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6481,21 +6472,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6505,10 +6496,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736372</v>
       </c>
       <c r="R58" t="n">
-        <v>7413089</v>
+        <v>7413070</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6567,10 +6558,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786920</v>
+        <v>122786887</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6579,38 +6570,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736393</v>
+        <v>736375</v>
       </c>
       <c r="R59" t="n">
-        <v>7413048</v>
+        <v>7413284</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6643,6 +6638,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R60" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R61" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -3043,10 +3043,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692908</v>
+        <v>122692855</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3055,25 +3055,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736202</v>
+        <v>736124</v>
       </c>
       <c r="R25" t="n">
-        <v>7413250</v>
+        <v>7412945</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3119,11 +3119,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3150,10 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692914</v>
+        <v>122692908</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3162,25 +3157,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3190,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736141</v>
+        <v>736202</v>
       </c>
       <c r="R26" t="n">
-        <v>7413319</v>
+        <v>7413250</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3228,13 +3223,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3253,7 +3252,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692916</v>
+        <v>122692914</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3293,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736092</v>
+        <v>736141</v>
       </c>
       <c r="R27" t="n">
-        <v>7413264</v>
+        <v>7413319</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3356,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692855</v>
+        <v>122692916</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3372,21 +3371,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736124</v>
+        <v>736092</v>
       </c>
       <c r="R28" t="n">
-        <v>7412945</v>
+        <v>7413264</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3440,6 +3439,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786874</v>
+        <v>122786922</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736381</v>
+        <v>736463</v>
       </c>
       <c r="R48" t="n">
-        <v>7413321</v>
+        <v>7413234</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5483,11 +5483,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5514,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786922</v>
+        <v>122786874</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,21 +5525,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5554,10 +5549,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736463</v>
+        <v>736381</v>
       </c>
       <c r="R49" t="n">
-        <v>7413234</v>
+        <v>7413321</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5590,6 +5585,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786896</v>
+        <v>122786919</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6370,21 +6370,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736223</v>
+        <v>736372</v>
       </c>
       <c r="R57" t="n">
-        <v>7413089</v>
+        <v>7413070</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786919</v>
+        <v>122786896</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736372</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>7413070</v>
+        <v>7413089</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -6354,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786919</v>
+        <v>122786896</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6370,21 +6370,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736372</v>
+        <v>736223</v>
       </c>
       <c r="R57" t="n">
-        <v>7413070</v>
+        <v>7413089</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786896</v>
+        <v>122786919</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736372</v>
       </c>
       <c r="R58" t="n">
-        <v>7413089</v>
+        <v>7413070</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -4586,10 +4586,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692856</v>
+        <v>122692859</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,25 +4598,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736114</v>
+        <v>736141</v>
       </c>
       <c r="R40" t="n">
-        <v>7412934</v>
+        <v>7413297</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692859</v>
+        <v>122692860</v>
       </c>
       <c r="B41" t="n">
         <v>56688</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736141</v>
+        <v>736132</v>
       </c>
       <c r="R41" t="n">
-        <v>7413297</v>
+        <v>7412974</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4764,6 +4764,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4790,10 +4795,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692860</v>
+        <v>122692856</v>
       </c>
       <c r="B42" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4802,25 +4807,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4830,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736132</v>
+        <v>736114</v>
       </c>
       <c r="R42" t="n">
-        <v>7412974</v>
+        <v>7412934</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4866,11 +4871,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692863</v>
+        <v>122692874</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736167</v>
+        <v>736203</v>
       </c>
       <c r="R2" t="n">
-        <v>7413243</v>
+        <v>7412940</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,17 +753,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692906</v>
+        <v>122692896</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736295</v>
+        <v>736227</v>
       </c>
       <c r="R3" t="n">
-        <v>7412988</v>
+        <v>7413172</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -866,7 +862,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692896</v>
+        <v>122692851</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736227</v>
+        <v>736115</v>
       </c>
       <c r="R4" t="n">
-        <v>7413172</v>
+        <v>7412928</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692877</v>
+        <v>122692861</v>
       </c>
       <c r="B5" t="n">
-        <v>57627</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,25 +994,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103022</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736170</v>
+        <v>736142</v>
       </c>
       <c r="R5" t="n">
-        <v>7413160</v>
+        <v>7413297</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1089,7 +1084,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692905</v>
+        <v>122692897</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1129,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736175</v>
+        <v>736248</v>
       </c>
       <c r="R6" t="n">
-        <v>7413127</v>
+        <v>7413169</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1191,7 +1186,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692913</v>
+        <v>122692916</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1231,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736262</v>
+        <v>736092</v>
       </c>
       <c r="R7" t="n">
-        <v>7413022</v>
+        <v>7413264</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1294,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692887</v>
+        <v>122692906</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1310,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735969</v>
+        <v>736295</v>
       </c>
       <c r="R8" t="n">
-        <v>7413433</v>
+        <v>7412988</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692892</v>
+        <v>122692850</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,21 +1408,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735982</v>
+        <v>736028</v>
       </c>
       <c r="R9" t="n">
-        <v>7413172</v>
+        <v>7413218</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1499,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692879</v>
+        <v>122692866</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,21 +1510,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1539,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736253</v>
+        <v>736167</v>
       </c>
       <c r="R10" t="n">
-        <v>7413052</v>
+        <v>7413025</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1583,7 +1578,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1602,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692888</v>
+        <v>122692865</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1612,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736141</v>
+        <v>736116</v>
       </c>
       <c r="R11" t="n">
-        <v>7413344</v>
+        <v>7412997</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1686,7 +1680,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692868</v>
+        <v>122692859</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1710,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736267</v>
+        <v>736141</v>
       </c>
       <c r="R12" t="n">
-        <v>7413160</v>
+        <v>7413297</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1781,11 +1774,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1800,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692893</v>
+        <v>122692899</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1852,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735982</v>
+        <v>736253</v>
       </c>
       <c r="R13" t="n">
-        <v>7413229</v>
+        <v>7413096</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1914,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692901</v>
+        <v>122692877</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57627</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1918,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736256</v>
+        <v>736170</v>
       </c>
       <c r="R14" t="n">
-        <v>7413074</v>
+        <v>7413160</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2016,10 +2004,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692880</v>
+        <v>122692908</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2016,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736205</v>
+        <v>736202</v>
       </c>
       <c r="R15" t="n">
-        <v>7412943</v>
+        <v>7413250</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2094,13 +2082,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2119,10 +2111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692861</v>
+        <v>122692914</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,25 +2123,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736142</v>
+        <v>736141</v>
       </c>
       <c r="R16" t="n">
-        <v>7413297</v>
+        <v>7413319</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2203,6 +2195,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2221,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692890</v>
+        <v>122692893</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2261,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736078</v>
+        <v>735982</v>
       </c>
       <c r="R17" t="n">
-        <v>7413098</v>
+        <v>7413229</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2323,7 +2316,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692889</v>
+        <v>122692900</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2363,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736006</v>
+        <v>736268</v>
       </c>
       <c r="R18" t="n">
-        <v>7413410</v>
+        <v>7413074</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2407,7 +2400,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2426,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692902</v>
+        <v>122692863</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,25 +2430,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736287</v>
+        <v>736167</v>
       </c>
       <c r="R19" t="n">
-        <v>7412989</v>
+        <v>7413243</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2502,6 +2494,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692900</v>
+        <v>122692862</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2568,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736268</v>
+        <v>735946</v>
       </c>
       <c r="R20" t="n">
-        <v>7413074</v>
+        <v>7413485</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2604,6 +2601,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,7 +2632,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692904</v>
+        <v>122692902</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2670,10 +2672,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736171</v>
+        <v>736287</v>
       </c>
       <c r="R21" t="n">
-        <v>7412886</v>
+        <v>7412989</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2732,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692852</v>
+        <v>122692880</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736126</v>
+        <v>736205</v>
       </c>
       <c r="R22" t="n">
-        <v>7412904</v>
+        <v>7412943</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2816,6 +2818,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2834,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692862</v>
+        <v>122692853</v>
       </c>
       <c r="B23" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2846,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2874,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735946</v>
+        <v>736120</v>
       </c>
       <c r="R23" t="n">
-        <v>7413485</v>
+        <v>7412935</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2910,11 +2913,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2941,7 +2939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692897</v>
+        <v>122692888</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2981,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736248</v>
+        <v>736141</v>
       </c>
       <c r="R24" t="n">
-        <v>7413169</v>
+        <v>7413344</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3025,6 +3023,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3043,10 +3042,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692855</v>
+        <v>122692913</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,21 +3058,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3083,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736124</v>
+        <v>736262</v>
       </c>
       <c r="R25" t="n">
-        <v>7412945</v>
+        <v>7413022</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3127,6 +3126,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692908</v>
+        <v>122692860</v>
       </c>
       <c r="B26" t="n">
         <v>56688</v>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736202</v>
+        <v>736132</v>
       </c>
       <c r="R26" t="n">
-        <v>7413250</v>
+        <v>7412974</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692914</v>
+        <v>122692905</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736141</v>
+        <v>736175</v>
       </c>
       <c r="R27" t="n">
-        <v>7413319</v>
+        <v>7413127</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3336,7 +3336,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3355,7 +3354,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692916</v>
+        <v>122692887</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3395,10 +3394,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736092</v>
+        <v>735969</v>
       </c>
       <c r="R28" t="n">
-        <v>7413264</v>
+        <v>7413433</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3458,7 +3457,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692886</v>
+        <v>122692891</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3492,19 +3491,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736116</v>
+        <v>736029</v>
       </c>
       <c r="R29" t="n">
-        <v>7412995</v>
+        <v>7413135</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3545,7 +3541,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3564,7 +3559,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692851</v>
+        <v>122692855</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3604,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736115</v>
+        <v>736124</v>
       </c>
       <c r="R30" t="n">
-        <v>7412928</v>
+        <v>7412945</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3666,7 +3661,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692866</v>
+        <v>122692864</v>
       </c>
       <c r="B31" t="n">
         <v>57631</v>
@@ -3706,10 +3701,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736167</v>
+        <v>736292</v>
       </c>
       <c r="R31" t="n">
-        <v>7413025</v>
+        <v>7412983</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3768,10 +3763,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692874</v>
+        <v>122692852</v>
       </c>
       <c r="B32" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3784,21 +3779,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736203</v>
+        <v>736126</v>
       </c>
       <c r="R32" t="n">
-        <v>7412940</v>
+        <v>7412904</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3852,7 +3847,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3871,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692899</v>
+        <v>122692892</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -3911,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736253</v>
+        <v>735982</v>
       </c>
       <c r="R33" t="n">
-        <v>7413096</v>
+        <v>7413172</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3973,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692853</v>
+        <v>122692879</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3989,21 +3983,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4013,10 +4007,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736120</v>
+        <v>736253</v>
       </c>
       <c r="R34" t="n">
-        <v>7412935</v>
+        <v>7413052</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,6 +4051,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4075,10 +4070,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692876</v>
+        <v>122692886</v>
       </c>
       <c r="B35" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4087,38 +4082,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736253</v>
+        <v>736116</v>
       </c>
       <c r="R35" t="n">
-        <v>7413052</v>
+        <v>7412995</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4159,6 +4157,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4177,10 +4176,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692867</v>
+        <v>122692903</v>
       </c>
       <c r="B36" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4193,21 +4192,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4217,10 +4216,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736165</v>
+        <v>736135</v>
       </c>
       <c r="R36" t="n">
-        <v>7413161</v>
+        <v>7412970</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4279,7 +4278,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692915</v>
+        <v>122692904</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4319,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736095</v>
+        <v>736171</v>
       </c>
       <c r="R37" t="n">
-        <v>7413383</v>
+        <v>7412886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4363,7 +4362,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4382,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692903</v>
+        <v>122692876</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4394,25 +4392,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736135</v>
+        <v>736253</v>
       </c>
       <c r="R38" t="n">
-        <v>7412970</v>
+        <v>7413052</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4484,7 +4482,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692850</v>
+        <v>122692856</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4524,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736028</v>
+        <v>736114</v>
       </c>
       <c r="R39" t="n">
-        <v>7413218</v>
+        <v>7412934</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4586,10 +4584,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692859</v>
+        <v>122692867</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4598,25 +4596,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4626,10 +4624,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736141</v>
+        <v>736165</v>
       </c>
       <c r="R40" t="n">
-        <v>7413297</v>
+        <v>7413161</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4688,10 +4686,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692860</v>
+        <v>122692889</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4700,25 +4698,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4728,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736132</v>
+        <v>736006</v>
       </c>
       <c r="R41" t="n">
-        <v>7412974</v>
+        <v>7413410</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4766,17 +4764,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4795,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692856</v>
+        <v>122692890</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,21 +4805,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,10 +4829,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736114</v>
+        <v>736078</v>
       </c>
       <c r="R42" t="n">
-        <v>7412934</v>
+        <v>7413098</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4897,10 +4891,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692865</v>
+        <v>122692901</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,21 +4907,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4937,10 +4931,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736116</v>
+        <v>736256</v>
       </c>
       <c r="R43" t="n">
-        <v>7412997</v>
+        <v>7413074</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4999,10 +4993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692864</v>
+        <v>122692915</v>
       </c>
       <c r="B44" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5009,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5033,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736292</v>
+        <v>736095</v>
       </c>
       <c r="R44" t="n">
-        <v>7412983</v>
+        <v>7413383</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5083,6 +5077,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5101,7 +5096,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692891</v>
+        <v>122692895</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5141,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736029</v>
+        <v>736222</v>
       </c>
       <c r="R45" t="n">
-        <v>7413135</v>
+        <v>7413197</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5203,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692895</v>
+        <v>122692868</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5214,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736222</v>
+        <v>736267</v>
       </c>
       <c r="R46" t="n">
-        <v>7413197</v>
+        <v>7413160</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5279,6 +5274,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5305,7 +5305,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786920</v>
+        <v>122786919</v>
       </c>
       <c r="B47" t="n">
         <v>78766</v>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736393</v>
+        <v>736372</v>
       </c>
       <c r="R47" t="n">
-        <v>7413048</v>
+        <v>7413070</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5407,7 +5407,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786922</v>
+        <v>122786920</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736463</v>
+        <v>736393</v>
       </c>
       <c r="R48" t="n">
-        <v>7413234</v>
+        <v>7413048</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5616,10 +5616,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786921</v>
+        <v>122786896</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,21 +5632,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736417</v>
+        <v>736223</v>
       </c>
       <c r="R50" t="n">
-        <v>7413130</v>
+        <v>7413089</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5718,10 +5718,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786873</v>
+        <v>122786922</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736260</v>
+        <v>736463</v>
       </c>
       <c r="R51" t="n">
-        <v>7413219</v>
+        <v>7413234</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5794,11 +5794,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5825,10 +5820,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786904</v>
+        <v>122786872</v>
       </c>
       <c r="B52" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5837,20 +5832,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5865,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736358</v>
+        <v>736447</v>
       </c>
       <c r="R52" t="n">
-        <v>7413327</v>
+        <v>7413232</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5901,6 +5896,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5927,7 +5927,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786872</v>
+        <v>122786871</v>
       </c>
       <c r="B53" t="n">
         <v>57478</v>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736447</v>
+        <v>736468</v>
       </c>
       <c r="R53" t="n">
-        <v>7413232</v>
+        <v>7413177</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6034,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786871</v>
+        <v>122786923</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736468</v>
+        <v>736316</v>
       </c>
       <c r="R54" t="n">
-        <v>7413177</v>
+        <v>7413295</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6110,11 +6110,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6141,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786888</v>
+        <v>122786904</v>
       </c>
       <c r="B55" t="n">
-        <v>57631</v>
+        <v>57589</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6153,32 +6148,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
@@ -6221,11 +6212,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6252,10 +6238,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786923</v>
+        <v>122786887</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6264,38 +6250,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736316</v>
+        <v>736375</v>
       </c>
       <c r="R56" t="n">
-        <v>7413295</v>
+        <v>7413284</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6328,6 +6318,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6354,10 +6349,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786896</v>
+        <v>122786873</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6370,16 +6365,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6394,10 +6389,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736223</v>
+        <v>736260</v>
       </c>
       <c r="R57" t="n">
-        <v>7413089</v>
+        <v>7413219</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6430,6 +6425,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6456,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786919</v>
+        <v>122786888</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,34 +6472,38 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736372</v>
+        <v>736358</v>
       </c>
       <c r="R58" t="n">
-        <v>7413070</v>
+        <v>7413327</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6532,6 +6536,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6558,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786887</v>
+        <v>122786921</v>
       </c>
       <c r="B59" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,42 +6579,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736375</v>
+        <v>736417</v>
       </c>
       <c r="R59" t="n">
-        <v>7413284</v>
+        <v>7413130</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6638,11 +6643,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R60" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R61" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692897</v>
+        <v>122692906</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736248</v>
+        <v>736295</v>
       </c>
       <c r="R6" t="n">
-        <v>7413169</v>
+        <v>7412988</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,6 +1168,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692916</v>
+        <v>122692850</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736092</v>
+        <v>736028</v>
       </c>
       <c r="R7" t="n">
-        <v>7413264</v>
+        <v>7413218</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1270,7 +1271,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692906</v>
+        <v>122692897</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736295</v>
+        <v>736248</v>
       </c>
       <c r="R8" t="n">
-        <v>7412988</v>
+        <v>7413169</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,7 +1373,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1392,10 +1391,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692850</v>
+        <v>122692916</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,21 +1407,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736028</v>
+        <v>736092</v>
       </c>
       <c r="R9" t="n">
-        <v>7413218</v>
+        <v>7413264</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1476,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692859</v>
+        <v>122692899</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736141</v>
+        <v>736253</v>
       </c>
       <c r="R12" t="n">
-        <v>7413297</v>
+        <v>7413096</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692899</v>
+        <v>122692859</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1812,25 +1812,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736253</v>
+        <v>736141</v>
       </c>
       <c r="R13" t="n">
-        <v>7413096</v>
+        <v>7413297</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692913</v>
+        <v>122692860</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3054,25 +3054,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736262</v>
+        <v>736132</v>
       </c>
       <c r="R25" t="n">
-        <v>7413022</v>
+        <v>7412974</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3120,13 +3120,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3145,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692860</v>
+        <v>122692913</v>
       </c>
       <c r="B26" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,25 +3161,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3185,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736132</v>
+        <v>736262</v>
       </c>
       <c r="R26" t="n">
-        <v>7412974</v>
+        <v>7413022</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3223,17 +3227,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692856</v>
+        <v>122692889</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,21 +4498,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736114</v>
+        <v>736006</v>
       </c>
       <c r="R39" t="n">
-        <v>7412934</v>
+        <v>7413410</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4566,6 +4566,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4584,10 +4585,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692867</v>
+        <v>122692890</v>
       </c>
       <c r="B40" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4600,21 +4601,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4624,10 +4625,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736165</v>
+        <v>736078</v>
       </c>
       <c r="R40" t="n">
-        <v>7413161</v>
+        <v>7413098</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4686,7 +4687,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692889</v>
+        <v>122692901</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736006</v>
+        <v>736256</v>
       </c>
       <c r="R41" t="n">
-        <v>7413410</v>
+        <v>7413074</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4770,7 +4771,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692890</v>
+        <v>122692856</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4805,21 +4805,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736078</v>
+        <v>736114</v>
       </c>
       <c r="R42" t="n">
-        <v>7413098</v>
+        <v>7412934</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4891,10 +4891,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692901</v>
+        <v>122692867</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4907,21 +4907,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736256</v>
+        <v>736165</v>
       </c>
       <c r="R43" t="n">
-        <v>7413074</v>
+        <v>7413161</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786871</v>
+        <v>122786904</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5939,20 +5939,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736468</v>
+        <v>736358</v>
       </c>
       <c r="R53" t="n">
-        <v>7413177</v>
+        <v>7413327</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6003,11 +6003,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6136,10 +6131,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786904</v>
+        <v>122786871</v>
       </c>
       <c r="B55" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,20 +6143,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6176,10 +6171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736358</v>
+        <v>736468</v>
       </c>
       <c r="R55" t="n">
-        <v>7413327</v>
+        <v>7413177</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6212,6 +6207,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1698,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692899</v>
+        <v>122692859</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736253</v>
+        <v>736141</v>
       </c>
       <c r="R12" t="n">
-        <v>7413096</v>
+        <v>7413297</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692859</v>
+        <v>122692899</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1812,25 +1812,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736141</v>
+        <v>736253</v>
       </c>
       <c r="R13" t="n">
-        <v>7413297</v>
+        <v>7413096</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692908</v>
+        <v>122692914</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2016,25 +2016,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736202</v>
+        <v>736141</v>
       </c>
       <c r="R15" t="n">
-        <v>7413250</v>
+        <v>7413319</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,17 +2082,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2111,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692914</v>
+        <v>122692908</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2123,25 +2119,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2151,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736141</v>
+        <v>736202</v>
       </c>
       <c r="R16" t="n">
-        <v>7413319</v>
+        <v>7413250</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2189,13 +2185,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692863</v>
+        <v>122692902</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736167</v>
+        <v>736287</v>
       </c>
       <c r="R19" t="n">
-        <v>7413243</v>
+        <v>7412989</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2494,11 +2494,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2525,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692862</v>
+        <v>122692880</v>
       </c>
       <c r="B20" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735946</v>
+        <v>736205</v>
       </c>
       <c r="R20" t="n">
-        <v>7413485</v>
+        <v>7412943</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2603,17 +2598,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692902</v>
+        <v>122692863</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736287</v>
+        <v>736167</v>
       </c>
       <c r="R21" t="n">
-        <v>7412989</v>
+        <v>7413243</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2708,6 +2699,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2734,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692880</v>
+        <v>122692862</v>
       </c>
       <c r="B22" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2746,25 +2742,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2774,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736205</v>
+        <v>735946</v>
       </c>
       <c r="R22" t="n">
-        <v>7412943</v>
+        <v>7413485</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2812,13 +2808,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -5927,10 +5927,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786904</v>
+        <v>122786871</v>
       </c>
       <c r="B53" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5939,20 +5939,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736358</v>
+        <v>736468</v>
       </c>
       <c r="R53" t="n">
-        <v>7413327</v>
+        <v>7413177</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6003,6 +6003,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6131,10 +6136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786871</v>
+        <v>122786904</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6143,20 +6148,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6171,10 +6176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736468</v>
+        <v>736358</v>
       </c>
       <c r="R55" t="n">
-        <v>7413177</v>
+        <v>7413327</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6207,11 +6212,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692874</v>
+        <v>122692880</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736203</v>
+        <v>736205</v>
       </c>
       <c r="R2" t="n">
-        <v>7412940</v>
+        <v>7412943</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692896</v>
+        <v>122692899</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736227</v>
+        <v>736253</v>
       </c>
       <c r="R3" t="n">
-        <v>7413172</v>
+        <v>7413096</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692851</v>
+        <v>122692916</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736115</v>
+        <v>736092</v>
       </c>
       <c r="R4" t="n">
-        <v>7412928</v>
+        <v>7413264</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,6 +964,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692861</v>
+        <v>122692908</v>
       </c>
       <c r="B5" t="n">
         <v>56688</v>
@@ -1022,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736142</v>
+        <v>736202</v>
       </c>
       <c r="R5" t="n">
-        <v>7413297</v>
+        <v>7413250</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1058,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692906</v>
+        <v>122692862</v>
       </c>
       <c r="B6" t="n">
-        <v>82553</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1096,25 +1102,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736295</v>
+        <v>735946</v>
       </c>
       <c r="R6" t="n">
-        <v>7412988</v>
+        <v>7413485</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1162,13 +1168,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1289,7 +1299,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692897</v>
+        <v>122692890</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1329,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736248</v>
+        <v>736078</v>
       </c>
       <c r="R8" t="n">
-        <v>7413169</v>
+        <v>7413098</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1391,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692916</v>
+        <v>122692865</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,21 +1417,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736092</v>
+        <v>736116</v>
       </c>
       <c r="R9" t="n">
-        <v>7413264</v>
+        <v>7412997</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1475,7 +1485,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692866</v>
+        <v>122692861</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1506,25 +1515,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736167</v>
+        <v>736142</v>
       </c>
       <c r="R10" t="n">
-        <v>7413025</v>
+        <v>7413297</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1596,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692865</v>
+        <v>122692889</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1612,21 +1621,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736116</v>
+        <v>736006</v>
       </c>
       <c r="R11" t="n">
-        <v>7412997</v>
+        <v>7413410</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1680,6 +1689,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1698,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692859</v>
+        <v>122692903</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1710,25 +1720,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736141</v>
+        <v>736135</v>
       </c>
       <c r="R12" t="n">
-        <v>7413297</v>
+        <v>7412970</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1800,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692899</v>
+        <v>122692864</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1816,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736253</v>
+        <v>736292</v>
       </c>
       <c r="R13" t="n">
-        <v>7413096</v>
+        <v>7412983</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1902,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692877</v>
+        <v>122692915</v>
       </c>
       <c r="B14" t="n">
-        <v>57627</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1918,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736170</v>
+        <v>736095</v>
       </c>
       <c r="R14" t="n">
-        <v>7413160</v>
+        <v>7413383</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1986,6 +1996,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2004,7 +2015,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692914</v>
+        <v>122692892</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2044,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736141</v>
+        <v>735982</v>
       </c>
       <c r="R15" t="n">
-        <v>7413319</v>
+        <v>7413172</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2088,7 +2099,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2107,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692908</v>
+        <v>122692896</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,25 +2129,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2147,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736202</v>
+        <v>736227</v>
       </c>
       <c r="R16" t="n">
-        <v>7413250</v>
+        <v>7413172</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2183,11 +2193,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692893</v>
+        <v>122692891</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2254,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735982</v>
+        <v>736029</v>
       </c>
       <c r="R17" t="n">
-        <v>7413229</v>
+        <v>7413135</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2316,7 +2321,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692900</v>
+        <v>122692895</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2356,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736268</v>
+        <v>736222</v>
       </c>
       <c r="R18" t="n">
-        <v>7413074</v>
+        <v>7413197</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2418,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692902</v>
+        <v>122692874</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736287</v>
+        <v>736203</v>
       </c>
       <c r="R19" t="n">
-        <v>7412989</v>
+        <v>7412940</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2502,6 +2507,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2520,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692880</v>
+        <v>122692906</v>
       </c>
       <c r="B20" t="n">
-        <v>78502</v>
+        <v>82553</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2542,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736205</v>
+        <v>736295</v>
       </c>
       <c r="R20" t="n">
-        <v>7412943</v>
+        <v>7412988</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2623,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692863</v>
+        <v>122692887</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736167</v>
+        <v>735969</v>
       </c>
       <c r="R21" t="n">
-        <v>7413243</v>
+        <v>7413433</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2701,17 +2707,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2730,7 +2732,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692862</v>
+        <v>122692860</v>
       </c>
       <c r="B22" t="n">
         <v>56688</v>
@@ -2770,10 +2772,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735946</v>
+        <v>736132</v>
       </c>
       <c r="R22" t="n">
-        <v>7413485</v>
+        <v>7412974</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2837,10 +2839,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692853</v>
+        <v>122692879</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2855,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2879,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736120</v>
+        <v>736253</v>
       </c>
       <c r="R23" t="n">
-        <v>7412935</v>
+        <v>7413052</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2921,6 +2923,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2939,7 +2942,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692888</v>
+        <v>122692902</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2979,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736141</v>
+        <v>736287</v>
       </c>
       <c r="R24" t="n">
-        <v>7413344</v>
+        <v>7412989</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3023,7 +3026,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3042,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692860</v>
+        <v>122692888</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3054,25 +3056,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3082,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736132</v>
+        <v>736141</v>
       </c>
       <c r="R25" t="n">
-        <v>7412974</v>
+        <v>7413344</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3120,17 +3122,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3149,7 +3147,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692913</v>
+        <v>122692901</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3189,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736262</v>
+        <v>736256</v>
       </c>
       <c r="R26" t="n">
-        <v>7413022</v>
+        <v>7413074</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3233,7 +3231,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3252,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692905</v>
+        <v>122692856</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3268,21 +3265,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3292,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736175</v>
+        <v>736114</v>
       </c>
       <c r="R27" t="n">
-        <v>7413127</v>
+        <v>7412934</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3354,7 +3351,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692887</v>
+        <v>122692900</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3394,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735969</v>
+        <v>736268</v>
       </c>
       <c r="R28" t="n">
-        <v>7413433</v>
+        <v>7413074</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3438,7 +3435,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3457,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692891</v>
+        <v>122692905</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3497,10 +3493,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736029</v>
+        <v>736175</v>
       </c>
       <c r="R29" t="n">
-        <v>7413135</v>
+        <v>7413127</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3559,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692855</v>
+        <v>122692893</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3575,21 +3571,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736124</v>
+        <v>735982</v>
       </c>
       <c r="R30" t="n">
-        <v>7412945</v>
+        <v>7413229</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3661,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692864</v>
+        <v>122692876</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>57589</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,25 +3669,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736292</v>
+        <v>736253</v>
       </c>
       <c r="R31" t="n">
-        <v>7412983</v>
+        <v>7413052</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3763,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692852</v>
+        <v>122692859</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,25 +3771,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3803,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736126</v>
+        <v>736141</v>
       </c>
       <c r="R32" t="n">
-        <v>7412904</v>
+        <v>7413297</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3865,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692892</v>
+        <v>122692867</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3881,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>735982</v>
+        <v>736165</v>
       </c>
       <c r="R33" t="n">
-        <v>7413172</v>
+        <v>7413161</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3967,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692879</v>
+        <v>122692897</v>
       </c>
       <c r="B34" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3983,21 +3979,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4007,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736253</v>
+        <v>736248</v>
       </c>
       <c r="R34" t="n">
-        <v>7413052</v>
+        <v>7413169</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4051,7 +4047,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4176,10 +4171,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692903</v>
+        <v>122692853</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4192,21 +4187,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4216,10 +4211,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736135</v>
+        <v>736120</v>
       </c>
       <c r="R36" t="n">
-        <v>7412970</v>
+        <v>7412935</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4278,10 +4273,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692904</v>
+        <v>122692851</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4294,21 +4289,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4318,10 +4313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736171</v>
+        <v>736115</v>
       </c>
       <c r="R37" t="n">
-        <v>7412886</v>
+        <v>7412928</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4380,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692876</v>
+        <v>122692914</v>
       </c>
       <c r="B38" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4392,25 +4387,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736253</v>
+        <v>736141</v>
       </c>
       <c r="R38" t="n">
-        <v>7413052</v>
+        <v>7413319</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4464,6 +4459,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4482,10 +4478,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692889</v>
+        <v>122692852</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,21 +4494,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4522,10 +4518,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736006</v>
+        <v>736126</v>
       </c>
       <c r="R39" t="n">
-        <v>7413410</v>
+        <v>7412904</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4566,7 +4562,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4585,10 +4580,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692890</v>
+        <v>122692877</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57627</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4601,21 +4596,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103022</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4625,10 +4620,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736078</v>
+        <v>736170</v>
       </c>
       <c r="R40" t="n">
-        <v>7413098</v>
+        <v>7413160</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4687,10 +4682,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692901</v>
+        <v>122692863</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,25 +4694,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4727,10 +4722,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736256</v>
+        <v>736167</v>
       </c>
       <c r="R41" t="n">
-        <v>7413074</v>
+        <v>7413243</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4763,6 +4758,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692856</v>
+        <v>122692868</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4805,16 +4805,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736114</v>
+        <v>736267</v>
       </c>
       <c r="R42" t="n">
-        <v>7412934</v>
+        <v>7413160</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4865,6 +4865,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,10 +4896,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692867</v>
+        <v>122692913</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4907,21 +4912,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4931,10 +4936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736165</v>
+        <v>736262</v>
       </c>
       <c r="R43" t="n">
-        <v>7413161</v>
+        <v>7413022</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4975,6 +4980,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4993,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692915</v>
+        <v>122692866</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5009,21 +5015,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5033,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736095</v>
+        <v>736167</v>
       </c>
       <c r="R44" t="n">
-        <v>7413383</v>
+        <v>7413025</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5077,7 +5083,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5096,7 +5101,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692895</v>
+        <v>122692904</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5136,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736222</v>
+        <v>736171</v>
       </c>
       <c r="R45" t="n">
-        <v>7413197</v>
+        <v>7412886</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5198,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692868</v>
+        <v>122692855</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5214,16 +5219,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5238,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736267</v>
+        <v>736124</v>
       </c>
       <c r="R46" t="n">
-        <v>7413160</v>
+        <v>7412945</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5274,11 +5279,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786919</v>
+        <v>122786871</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736372</v>
+        <v>736468</v>
       </c>
       <c r="R47" t="n">
-        <v>7413070</v>
+        <v>7413177</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5381,6 +5381,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5407,7 +5412,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786920</v>
+        <v>122786919</v>
       </c>
       <c r="B48" t="n">
         <v>78766</v>
@@ -5447,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736393</v>
+        <v>736372</v>
       </c>
       <c r="R48" t="n">
-        <v>7413048</v>
+        <v>7413070</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5509,10 +5514,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786874</v>
+        <v>122786888</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,34 +5530,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736381</v>
+        <v>736358</v>
       </c>
       <c r="R49" t="n">
-        <v>7413321</v>
+        <v>7413327</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5589,7 +5598,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5616,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786896</v>
+        <v>122786921</v>
       </c>
       <c r="B50" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,21 +5641,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5656,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736223</v>
+        <v>736417</v>
       </c>
       <c r="R50" t="n">
-        <v>7413089</v>
+        <v>7413130</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5718,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786922</v>
+        <v>122786872</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5734,21 +5743,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5758,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736463</v>
+        <v>736447</v>
       </c>
       <c r="R51" t="n">
-        <v>7413234</v>
+        <v>7413232</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5794,6 +5803,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5820,7 +5834,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786872</v>
+        <v>122786874</v>
       </c>
       <c r="B52" t="n">
         <v>57478</v>
@@ -5860,10 +5874,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736447</v>
+        <v>736381</v>
       </c>
       <c r="R52" t="n">
-        <v>7413232</v>
+        <v>7413321</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5927,10 +5941,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786871</v>
+        <v>122786922</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,21 +5957,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5967,10 +5981,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736468</v>
+        <v>736463</v>
       </c>
       <c r="R53" t="n">
-        <v>7413177</v>
+        <v>7413234</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6003,11 +6017,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6034,7 +6043,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786923</v>
+        <v>122786920</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6074,10 +6083,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736316</v>
+        <v>736393</v>
       </c>
       <c r="R54" t="n">
-        <v>7413295</v>
+        <v>7413048</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6136,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786904</v>
+        <v>122786887</v>
       </c>
       <c r="B55" t="n">
-        <v>57589</v>
+        <v>56688</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6152,34 +6161,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736358</v>
+        <v>736375</v>
       </c>
       <c r="R55" t="n">
-        <v>7413327</v>
+        <v>7413284</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6212,6 +6225,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6238,10 +6256,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786887</v>
+        <v>122786904</v>
       </c>
       <c r="B56" t="n">
-        <v>56688</v>
+        <v>57589</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6254,38 +6272,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736375</v>
+        <v>736358</v>
       </c>
       <c r="R56" t="n">
-        <v>7413284</v>
+        <v>7413327</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6318,11 +6332,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6349,10 +6358,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786873</v>
+        <v>122786923</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6365,21 +6374,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6389,10 +6398,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736260</v>
+        <v>736316</v>
       </c>
       <c r="R57" t="n">
-        <v>7413219</v>
+        <v>7413295</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6425,11 +6434,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6456,10 +6460,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786888</v>
+        <v>122786873</v>
       </c>
       <c r="B58" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,38 +6476,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736358</v>
+        <v>736260</v>
       </c>
       <c r="R58" t="n">
-        <v>7413327</v>
+        <v>7413219</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6567,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786921</v>
+        <v>122786896</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6583,21 +6583,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736417</v>
+        <v>736223</v>
       </c>
       <c r="R59" t="n">
-        <v>7413130</v>
+        <v>7413089</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R60" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R61" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692890</v>
+        <v>122692861</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,25 +1311,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736078</v>
+        <v>736142</v>
       </c>
       <c r="R8" t="n">
-        <v>7413098</v>
+        <v>7413297</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692865</v>
+        <v>122692890</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,21 +1417,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736116</v>
+        <v>736078</v>
       </c>
       <c r="R9" t="n">
-        <v>7412997</v>
+        <v>7413098</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692861</v>
+        <v>122692865</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,25 +1515,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736142</v>
+        <v>736116</v>
       </c>
       <c r="R10" t="n">
-        <v>7413297</v>
+        <v>7412997</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692859</v>
+        <v>122692853</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,25 +3771,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736141</v>
+        <v>736120</v>
       </c>
       <c r="R32" t="n">
-        <v>7413297</v>
+        <v>7412935</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692867</v>
+        <v>122692851</v>
       </c>
       <c r="B33" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736165</v>
+        <v>736115</v>
       </c>
       <c r="R33" t="n">
-        <v>7413161</v>
+        <v>7412928</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692853</v>
+        <v>122692859</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,25 +4183,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736120</v>
+        <v>736141</v>
       </c>
       <c r="R36" t="n">
-        <v>7412935</v>
+        <v>7413297</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692851</v>
+        <v>122692867</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,21 +4289,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736115</v>
+        <v>736165</v>
       </c>
       <c r="R37" t="n">
-        <v>7412928</v>
+        <v>7413161</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4682,10 +4682,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692863</v>
+        <v>122692868</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4694,25 +4694,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736167</v>
+        <v>736267</v>
       </c>
       <c r="R41" t="n">
-        <v>7413243</v>
+        <v>7413160</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Spår i snön</t>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692868</v>
+        <v>122692863</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,25 +4801,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736267</v>
+        <v>736167</v>
       </c>
       <c r="R42" t="n">
-        <v>7413160</v>
+        <v>7413243</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackspår på torrträd</t>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692880</v>
+        <v>122692906</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736205</v>
+        <v>736295</v>
       </c>
       <c r="R2" t="n">
-        <v>7412943</v>
+        <v>7412988</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692899</v>
+        <v>122692916</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736253</v>
+        <v>736092</v>
       </c>
       <c r="R3" t="n">
-        <v>7413096</v>
+        <v>7413264</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,6 +862,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,7 +881,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692916</v>
+        <v>122692890</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -920,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736092</v>
+        <v>736078</v>
       </c>
       <c r="R4" t="n">
-        <v>7413264</v>
+        <v>7413098</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +965,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692908</v>
+        <v>122692900</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -995,25 +995,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736202</v>
+        <v>736268</v>
       </c>
       <c r="R5" t="n">
-        <v>7413250</v>
+        <v>7413074</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,11 +1059,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692862</v>
+        <v>122692904</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1102,25 +1097,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735946</v>
+        <v>736171</v>
       </c>
       <c r="R6" t="n">
-        <v>7413485</v>
+        <v>7412886</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1166,11 +1161,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,7 +1187,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692850</v>
+        <v>122692853</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1237,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736028</v>
+        <v>736120</v>
       </c>
       <c r="R7" t="n">
-        <v>7413218</v>
+        <v>7412935</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,7 +1289,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692861</v>
+        <v>122692862</v>
       </c>
       <c r="B8" t="n">
         <v>56688</v>
@@ -1339,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736142</v>
+        <v>735946</v>
       </c>
       <c r="R8" t="n">
-        <v>7413297</v>
+        <v>7413485</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1375,6 +1365,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1396,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692890</v>
+        <v>122692899</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1441,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736078</v>
+        <v>736253</v>
       </c>
       <c r="R9" t="n">
-        <v>7413098</v>
+        <v>7413096</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692865</v>
+        <v>122692856</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1519,21 +1514,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736116</v>
+        <v>736114</v>
       </c>
       <c r="R10" t="n">
-        <v>7412997</v>
+        <v>7412934</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692889</v>
+        <v>122692865</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,21 +1616,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736006</v>
+        <v>736116</v>
       </c>
       <c r="R11" t="n">
-        <v>7413410</v>
+        <v>7412997</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1689,7 +1684,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1708,7 +1702,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692903</v>
+        <v>122692888</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1748,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736135</v>
+        <v>736141</v>
       </c>
       <c r="R12" t="n">
-        <v>7412970</v>
+        <v>7413344</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1792,6 +1786,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692864</v>
+        <v>122692859</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,25 +1817,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736292</v>
+        <v>736141</v>
       </c>
       <c r="R13" t="n">
-        <v>7412983</v>
+        <v>7413297</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692915</v>
+        <v>122692880</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1928,21 +1923,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736095</v>
+        <v>736205</v>
       </c>
       <c r="R14" t="n">
-        <v>7413383</v>
+        <v>7412943</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,7 +2010,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692892</v>
+        <v>122692905</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2055,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735982</v>
+        <v>736175</v>
       </c>
       <c r="R15" t="n">
-        <v>7413172</v>
+        <v>7413127</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,7 +2112,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692896</v>
+        <v>122692895</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2157,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736227</v>
+        <v>736222</v>
       </c>
       <c r="R16" t="n">
-        <v>7413172</v>
+        <v>7413197</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2219,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692891</v>
+        <v>122692867</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736029</v>
+        <v>736165</v>
       </c>
       <c r="R17" t="n">
-        <v>7413135</v>
+        <v>7413161</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,7 +2316,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692895</v>
+        <v>122692889</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2361,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736222</v>
+        <v>736006</v>
       </c>
       <c r="R18" t="n">
-        <v>7413197</v>
+        <v>7413410</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,6 +2400,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2423,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692874</v>
+        <v>122692864</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>57631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736203</v>
+        <v>736292</v>
       </c>
       <c r="R19" t="n">
-        <v>7412940</v>
+        <v>7412983</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2507,7 +2503,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2526,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692906</v>
+        <v>122692874</v>
       </c>
       <c r="B20" t="n">
-        <v>82553</v>
+        <v>78503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736295</v>
+        <v>736203</v>
       </c>
       <c r="R20" t="n">
-        <v>7412988</v>
+        <v>7412940</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692887</v>
+        <v>122692876</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2636,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735969</v>
+        <v>736253</v>
       </c>
       <c r="R21" t="n">
-        <v>7413433</v>
+        <v>7413052</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2713,7 +2708,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2732,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692860</v>
+        <v>122692851</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2744,25 +2738,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736132</v>
+        <v>736115</v>
       </c>
       <c r="R22" t="n">
-        <v>7412974</v>
+        <v>7412928</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2808,11 +2802,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2839,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692879</v>
+        <v>122692861</v>
       </c>
       <c r="B23" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2879,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736253</v>
+        <v>736142</v>
       </c>
       <c r="R23" t="n">
-        <v>7413052</v>
+        <v>7413297</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2923,7 +2912,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2942,7 +2930,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692902</v>
+        <v>122692886</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2976,16 +2964,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736287</v>
+        <v>736116</v>
       </c>
       <c r="R24" t="n">
-        <v>7412989</v>
+        <v>7412995</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,6 +3017,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3044,7 +3036,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692888</v>
+        <v>122692893</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3084,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736141</v>
+        <v>735982</v>
       </c>
       <c r="R25" t="n">
-        <v>7413344</v>
+        <v>7413229</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,7 +3120,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3147,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692901</v>
+        <v>122692855</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,21 +3154,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736256</v>
+        <v>736124</v>
       </c>
       <c r="R26" t="n">
-        <v>7413074</v>
+        <v>7412945</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3249,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692856</v>
+        <v>122692913</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,21 +3256,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736114</v>
+        <v>736262</v>
       </c>
       <c r="R27" t="n">
-        <v>7412934</v>
+        <v>7413022</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3333,6 +3324,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3351,7 +3343,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692900</v>
+        <v>122692914</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3391,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736268</v>
+        <v>736141</v>
       </c>
       <c r="R28" t="n">
-        <v>7413074</v>
+        <v>7413319</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3435,6 +3427,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3453,7 +3446,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692905</v>
+        <v>122692892</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3493,10 +3486,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736175</v>
+        <v>735982</v>
       </c>
       <c r="R29" t="n">
-        <v>7413127</v>
+        <v>7413172</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3555,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692893</v>
+        <v>122692852</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,21 +3564,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3595,10 +3588,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735982</v>
+        <v>736126</v>
       </c>
       <c r="R30" t="n">
-        <v>7413229</v>
+        <v>7412904</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3657,10 +3650,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692876</v>
+        <v>122692908</v>
       </c>
       <c r="B31" t="n">
-        <v>57589</v>
+        <v>56688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,21 +3666,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3690,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736253</v>
+        <v>736202</v>
       </c>
       <c r="R31" t="n">
-        <v>7413052</v>
+        <v>7413250</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3733,6 +3726,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,10 +3757,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692853</v>
+        <v>122692868</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,16 +3773,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3799,10 +3797,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736120</v>
+        <v>736267</v>
       </c>
       <c r="R32" t="n">
-        <v>7412935</v>
+        <v>7413160</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3835,6 +3833,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3861,10 +3864,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692851</v>
+        <v>122692877</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57627</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,21 +3880,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3904,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736115</v>
+        <v>736170</v>
       </c>
       <c r="R33" t="n">
-        <v>7412928</v>
+        <v>7413160</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3963,7 +3966,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692897</v>
+        <v>122692887</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4003,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736248</v>
+        <v>735969</v>
       </c>
       <c r="R34" t="n">
-        <v>7413169</v>
+        <v>7413433</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4047,6 +4050,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4065,7 +4069,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692886</v>
+        <v>122692896</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4099,19 +4103,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736116</v>
+        <v>736227</v>
       </c>
       <c r="R35" t="n">
-        <v>7412995</v>
+        <v>7413172</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4152,7 +4153,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692859</v>
+        <v>122692915</v>
       </c>
       <c r="B36" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,25 +4183,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736141</v>
+        <v>736095</v>
       </c>
       <c r="R36" t="n">
-        <v>7413297</v>
+        <v>7413383</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4255,6 +4255,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4273,10 +4274,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692867</v>
+        <v>122692897</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,21 +4290,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4313,10 +4314,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736165</v>
+        <v>736248</v>
       </c>
       <c r="R37" t="n">
-        <v>7413161</v>
+        <v>7413169</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4375,10 +4376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692914</v>
+        <v>122692866</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4391,21 +4392,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4415,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736141</v>
+        <v>736167</v>
       </c>
       <c r="R38" t="n">
-        <v>7413319</v>
+        <v>7413025</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4459,7 +4460,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4478,10 +4478,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692852</v>
+        <v>122692879</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,21 +4494,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736126</v>
+        <v>736253</v>
       </c>
       <c r="R39" t="n">
-        <v>7412904</v>
+        <v>7413052</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,6 +4562,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4580,10 +4581,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692877</v>
+        <v>122692902</v>
       </c>
       <c r="B40" t="n">
-        <v>57627</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4596,21 +4597,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4620,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736170</v>
+        <v>736287</v>
       </c>
       <c r="R40" t="n">
-        <v>7413160</v>
+        <v>7412989</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4682,10 +4683,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692868</v>
+        <v>122692863</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4694,25 +4695,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4722,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736267</v>
+        <v>736167</v>
       </c>
       <c r="R41" t="n">
-        <v>7413160</v>
+        <v>7413243</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4762,7 +4763,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackspår på torrträd</t>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4789,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692863</v>
+        <v>122692850</v>
       </c>
       <c r="B42" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4801,25 +4802,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4829,10 +4830,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736167</v>
+        <v>736028</v>
       </c>
       <c r="R42" t="n">
-        <v>7413243</v>
+        <v>7413218</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4865,11 +4866,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4896,7 +4892,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692913</v>
+        <v>122692891</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4936,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736262</v>
+        <v>736029</v>
       </c>
       <c r="R43" t="n">
-        <v>7413022</v>
+        <v>7413135</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4980,7 +4976,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4999,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692866</v>
+        <v>122692903</v>
       </c>
       <c r="B44" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,21 +5010,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5039,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736167</v>
+        <v>736135</v>
       </c>
       <c r="R44" t="n">
-        <v>7413025</v>
+        <v>7412970</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5101,7 +5096,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692904</v>
+        <v>122692901</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5141,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736171</v>
+        <v>736256</v>
       </c>
       <c r="R45" t="n">
-        <v>7412886</v>
+        <v>7413074</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5203,10 +5198,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692855</v>
+        <v>122692860</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5215,25 +5210,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5238,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736124</v>
+        <v>736132</v>
       </c>
       <c r="R46" t="n">
-        <v>7412945</v>
+        <v>7412974</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5279,6 +5274,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786871</v>
+        <v>122786904</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5317,20 +5317,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736468</v>
+        <v>736358</v>
       </c>
       <c r="R47" t="n">
-        <v>7413177</v>
+        <v>7413327</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5381,11 +5381,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5412,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786919</v>
+        <v>122786888</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,34 +5423,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736372</v>
+        <v>736358</v>
       </c>
       <c r="R48" t="n">
-        <v>7413070</v>
+        <v>7413327</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5488,6 +5487,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5514,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786888</v>
+        <v>122786919</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,38 +5534,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736358</v>
+        <v>736372</v>
       </c>
       <c r="R49" t="n">
-        <v>7413327</v>
+        <v>7413070</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5594,11 +5594,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5625,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786921</v>
+        <v>122786874</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,21 +5636,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5665,10 +5660,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736417</v>
+        <v>736381</v>
       </c>
       <c r="R50" t="n">
-        <v>7413130</v>
+        <v>7413321</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5701,6 +5696,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5834,10 +5834,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786874</v>
+        <v>122786923</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5850,21 +5850,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736381</v>
+        <v>736316</v>
       </c>
       <c r="R52" t="n">
-        <v>7413321</v>
+        <v>7413295</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5910,11 +5910,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5941,7 +5936,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786922</v>
+        <v>122786920</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -5981,10 +5976,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736463</v>
+        <v>736393</v>
       </c>
       <c r="R53" t="n">
-        <v>7413234</v>
+        <v>7413048</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6043,7 +6038,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786920</v>
+        <v>122786922</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6083,10 +6078,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736393</v>
+        <v>736463</v>
       </c>
       <c r="R54" t="n">
-        <v>7413048</v>
+        <v>7413234</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6145,10 +6140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786887</v>
+        <v>122786873</v>
       </c>
       <c r="B55" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6157,42 +6152,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736375</v>
+        <v>736260</v>
       </c>
       <c r="R55" t="n">
-        <v>7413284</v>
+        <v>7413219</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6229,7 +6220,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6256,10 +6247,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786904</v>
+        <v>122786871</v>
       </c>
       <c r="B56" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6268,20 +6259,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6296,10 +6287,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736358</v>
+        <v>736468</v>
       </c>
       <c r="R56" t="n">
-        <v>7413327</v>
+        <v>7413177</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6332,6 +6323,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6358,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786923</v>
+        <v>122786887</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6370,38 +6366,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736316</v>
+        <v>736375</v>
       </c>
       <c r="R57" t="n">
-        <v>7413295</v>
+        <v>7413284</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6434,6 +6434,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6460,10 +6465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786873</v>
+        <v>122786921</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6476,21 +6481,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6500,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736260</v>
+        <v>736417</v>
       </c>
       <c r="R58" t="n">
-        <v>7413219</v>
+        <v>7413130</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6536,11 +6541,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1600,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692865</v>
+        <v>122692888</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1616,21 +1616,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736116</v>
+        <v>736141</v>
       </c>
       <c r="R11" t="n">
-        <v>7412997</v>
+        <v>7413344</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1684,6 +1684,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1702,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692888</v>
+        <v>122692859</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1714,25 +1715,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,7 +1746,7 @@
         <v>736141</v>
       </c>
       <c r="R12" t="n">
-        <v>7413344</v>
+        <v>7413297</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1786,7 +1787,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692859</v>
+        <v>122692865</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,25 +1817,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736141</v>
+        <v>736116</v>
       </c>
       <c r="R13" t="n">
-        <v>7413297</v>
+        <v>7412997</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -983,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692900</v>
+        <v>122692904</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736268</v>
+        <v>736171</v>
       </c>
       <c r="R5" t="n">
-        <v>7413074</v>
+        <v>7412886</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692904</v>
+        <v>122692853</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736171</v>
+        <v>736120</v>
       </c>
       <c r="R6" t="n">
-        <v>7412886</v>
+        <v>7412935</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692853</v>
+        <v>122692862</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1199,25 +1199,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736120</v>
+        <v>735946</v>
       </c>
       <c r="R7" t="n">
-        <v>7412935</v>
+        <v>7413485</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1263,6 +1263,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692862</v>
+        <v>122692900</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1301,25 +1306,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1329,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735946</v>
+        <v>736268</v>
       </c>
       <c r="R8" t="n">
-        <v>7413485</v>
+        <v>7413074</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1365,11 +1370,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692888</v>
+        <v>122692859</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1612,25 +1612,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,7 +1643,7 @@
         <v>736141</v>
       </c>
       <c r="R11" t="n">
-        <v>7413344</v>
+        <v>7413297</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1684,7 +1684,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1702,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692859</v>
+        <v>122692865</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1715,25 +1714,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736141</v>
+        <v>736116</v>
       </c>
       <c r="R12" t="n">
-        <v>7413297</v>
+        <v>7412997</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1805,10 +1804,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692865</v>
+        <v>122692888</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,21 +1820,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736116</v>
+        <v>736141</v>
       </c>
       <c r="R13" t="n">
-        <v>7412997</v>
+        <v>7413344</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1889,6 +1888,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692906</v>
+        <v>122692891</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736295</v>
+        <v>736029</v>
       </c>
       <c r="R2" t="n">
-        <v>7412988</v>
+        <v>7413135</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692916</v>
+        <v>122692865</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736092</v>
+        <v>736116</v>
       </c>
       <c r="R3" t="n">
-        <v>7413264</v>
+        <v>7412997</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692890</v>
+        <v>122692879</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -921,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736078</v>
+        <v>736253</v>
       </c>
       <c r="R4" t="n">
-        <v>7413098</v>
+        <v>7413052</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -965,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -983,7 +982,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692904</v>
+        <v>122692895</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1023,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736171</v>
+        <v>736222</v>
       </c>
       <c r="R5" t="n">
-        <v>7412886</v>
+        <v>7413197</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1085,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692853</v>
+        <v>122692890</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736120</v>
+        <v>736078</v>
       </c>
       <c r="R6" t="n">
-        <v>7412935</v>
+        <v>7413098</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1187,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692862</v>
+        <v>122692896</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1199,25 +1198,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1227,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735946</v>
+        <v>736227</v>
       </c>
       <c r="R7" t="n">
-        <v>7413485</v>
+        <v>7413172</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1263,11 +1262,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1294,7 +1288,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692900</v>
+        <v>122692888</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1334,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736268</v>
+        <v>736141</v>
       </c>
       <c r="R8" t="n">
-        <v>7413074</v>
+        <v>7413344</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1378,6 +1372,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1396,7 +1391,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692899</v>
+        <v>122692914</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1436,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736253</v>
+        <v>736141</v>
       </c>
       <c r="R9" t="n">
-        <v>7413096</v>
+        <v>7413319</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1480,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1498,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692856</v>
+        <v>122692861</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1510,25 +1506,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736114</v>
+        <v>736142</v>
       </c>
       <c r="R10" t="n">
-        <v>7412934</v>
+        <v>7413297</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1600,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692859</v>
+        <v>122692880</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1612,25 +1608,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736141</v>
+        <v>736205</v>
       </c>
       <c r="R11" t="n">
-        <v>7413297</v>
+        <v>7412943</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1684,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1702,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692865</v>
+        <v>122692903</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1718,21 +1715,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736116</v>
+        <v>736135</v>
       </c>
       <c r="R12" t="n">
-        <v>7412997</v>
+        <v>7412970</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1804,7 +1801,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692888</v>
+        <v>122692913</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1844,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736141</v>
+        <v>736262</v>
       </c>
       <c r="R13" t="n">
-        <v>7413344</v>
+        <v>7413022</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1907,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692880</v>
+        <v>122692908</v>
       </c>
       <c r="B14" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1919,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736205</v>
+        <v>736202</v>
       </c>
       <c r="R14" t="n">
-        <v>7412943</v>
+        <v>7413250</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1985,13 +1982,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692905</v>
+        <v>122692901</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2050,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736175</v>
+        <v>736256</v>
       </c>
       <c r="R15" t="n">
-        <v>7413127</v>
+        <v>7413074</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2112,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692895</v>
+        <v>122692916</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2152,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736222</v>
+        <v>736092</v>
       </c>
       <c r="R16" t="n">
-        <v>7413197</v>
+        <v>7413264</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2196,6 +2197,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2214,10 +2216,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692867</v>
+        <v>122692886</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,34 +2232,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736165</v>
+        <v>736116</v>
       </c>
       <c r="R17" t="n">
-        <v>7413161</v>
+        <v>7412995</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2298,6 +2303,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692889</v>
+        <v>122692868</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736006</v>
+        <v>736267</v>
       </c>
       <c r="R18" t="n">
-        <v>7413410</v>
+        <v>7413160</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2394,13 +2400,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2419,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692864</v>
+        <v>122692859</v>
       </c>
       <c r="B19" t="n">
-        <v>57631</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736292</v>
+        <v>736141</v>
       </c>
       <c r="R19" t="n">
-        <v>7412983</v>
+        <v>7413297</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2521,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692874</v>
+        <v>122692906</v>
       </c>
       <c r="B20" t="n">
-        <v>78503</v>
+        <v>82553</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736203</v>
+        <v>736295</v>
       </c>
       <c r="R20" t="n">
-        <v>7412940</v>
+        <v>7412988</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2624,10 +2634,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692876</v>
+        <v>122692855</v>
       </c>
       <c r="B21" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2636,20 +2646,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2664,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736253</v>
+        <v>736124</v>
       </c>
       <c r="R21" t="n">
-        <v>7413052</v>
+        <v>7412945</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692851</v>
+        <v>122692876</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2738,20 +2748,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2766,10 +2776,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736115</v>
+        <v>736253</v>
       </c>
       <c r="R22" t="n">
-        <v>7412928</v>
+        <v>7413052</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2828,7 +2838,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692861</v>
+        <v>122692863</v>
       </c>
       <c r="B23" t="n">
         <v>56688</v>
@@ -2868,10 +2878,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736142</v>
+        <v>736167</v>
       </c>
       <c r="R23" t="n">
-        <v>7413297</v>
+        <v>7413243</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2904,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2930,7 +2945,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692886</v>
+        <v>122692900</v>
       </c>
       <c r="B24" t="n">
         <v>78766</v>
@@ -2964,19 +2979,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736116</v>
+        <v>736268</v>
       </c>
       <c r="R24" t="n">
-        <v>7412995</v>
+        <v>7413074</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3017,7 +3029,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3036,7 +3047,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692893</v>
+        <v>122692897</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3076,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735982</v>
+        <v>736248</v>
       </c>
       <c r="R25" t="n">
-        <v>7413229</v>
+        <v>7413169</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3138,7 +3149,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692855</v>
+        <v>122692851</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3178,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736124</v>
+        <v>736115</v>
       </c>
       <c r="R26" t="n">
-        <v>7412945</v>
+        <v>7412928</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3240,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692913</v>
+        <v>122692856</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3256,21 +3267,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3280,10 +3291,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736262</v>
+        <v>736114</v>
       </c>
       <c r="R27" t="n">
-        <v>7413022</v>
+        <v>7412934</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3324,7 +3335,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3353,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692914</v>
+        <v>122692852</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,21 +3369,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3393,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736141</v>
+        <v>736126</v>
       </c>
       <c r="R28" t="n">
-        <v>7413319</v>
+        <v>7412904</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3427,7 +3437,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3446,7 +3455,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692892</v>
+        <v>122692905</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3486,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735982</v>
+        <v>736175</v>
       </c>
       <c r="R29" t="n">
-        <v>7413172</v>
+        <v>7413127</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3548,10 +3557,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692852</v>
+        <v>122692904</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3564,21 +3573,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3588,10 +3597,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736126</v>
+        <v>736171</v>
       </c>
       <c r="R30" t="n">
-        <v>7412904</v>
+        <v>7412886</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3650,10 +3659,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692908</v>
+        <v>122692867</v>
       </c>
       <c r="B31" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3662,25 +3671,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3690,10 +3699,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736202</v>
+        <v>736165</v>
       </c>
       <c r="R31" t="n">
-        <v>7413250</v>
+        <v>7413161</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3726,11 +3735,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3757,10 +3761,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692868</v>
+        <v>122692877</v>
       </c>
       <c r="B32" t="n">
-        <v>57494</v>
+        <v>57627</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3773,21 +3777,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103022</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3797,7 +3801,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736267</v>
+        <v>736170</v>
       </c>
       <c r="R32" t="n">
         <v>7413160</v>
@@ -3833,11 +3837,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,10 +3863,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692877</v>
+        <v>122692915</v>
       </c>
       <c r="B33" t="n">
-        <v>57627</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3880,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103022</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3904,10 +3903,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736170</v>
+        <v>736095</v>
       </c>
       <c r="R33" t="n">
-        <v>7413160</v>
+        <v>7413383</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3948,6 +3947,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692887</v>
+        <v>122692860</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>735969</v>
+        <v>736132</v>
       </c>
       <c r="R34" t="n">
-        <v>7413433</v>
+        <v>7412974</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4044,13 +4044,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4069,10 +4073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692896</v>
+        <v>122692850</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4085,21 +4089,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4109,10 +4113,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736227</v>
+        <v>736028</v>
       </c>
       <c r="R35" t="n">
-        <v>7413172</v>
+        <v>7413218</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4171,7 +4175,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692915</v>
+        <v>122692893</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4211,10 +4215,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736095</v>
+        <v>735982</v>
       </c>
       <c r="R36" t="n">
-        <v>7413383</v>
+        <v>7413229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4255,7 +4259,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4274,7 +4277,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692897</v>
+        <v>122692892</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4314,10 +4317,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736248</v>
+        <v>735982</v>
       </c>
       <c r="R37" t="n">
-        <v>7413169</v>
+        <v>7413172</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4376,10 +4379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692866</v>
+        <v>122692899</v>
       </c>
       <c r="B38" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4392,21 +4395,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736167</v>
+        <v>736253</v>
       </c>
       <c r="R38" t="n">
-        <v>7413025</v>
+        <v>7413096</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4478,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692879</v>
+        <v>122692866</v>
       </c>
       <c r="B39" t="n">
-        <v>78502</v>
+        <v>57631</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,21 +4497,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4518,10 +4521,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736253</v>
+        <v>736167</v>
       </c>
       <c r="R39" t="n">
-        <v>7413052</v>
+        <v>7413025</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,7 +4565,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4581,10 +4583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692902</v>
+        <v>122692874</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,21 +4599,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4621,10 +4623,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736287</v>
+        <v>736203</v>
       </c>
       <c r="R40" t="n">
-        <v>7412989</v>
+        <v>7412940</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4665,6 +4667,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4683,10 +4686,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692863</v>
+        <v>122692887</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4695,25 +4698,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736167</v>
+        <v>735969</v>
       </c>
       <c r="R41" t="n">
-        <v>7413243</v>
+        <v>7413433</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4761,17 +4764,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4790,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692850</v>
+        <v>122692889</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4806,21 +4805,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4830,10 +4829,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736028</v>
+        <v>736006</v>
       </c>
       <c r="R42" t="n">
-        <v>7413218</v>
+        <v>7413410</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4874,6 +4873,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4892,7 +4892,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692891</v>
+        <v>122692902</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736029</v>
+        <v>736287</v>
       </c>
       <c r="R43" t="n">
-        <v>7413135</v>
+        <v>7412989</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4994,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692903</v>
+        <v>122692853</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736135</v>
+        <v>736120</v>
       </c>
       <c r="R44" t="n">
-        <v>7412970</v>
+        <v>7412935</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692901</v>
+        <v>122692862</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5108,25 +5108,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736256</v>
+        <v>735946</v>
       </c>
       <c r="R45" t="n">
-        <v>7413074</v>
+        <v>7413485</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5172,6 +5172,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5198,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692860</v>
+        <v>122692864</v>
       </c>
       <c r="B46" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5210,25 +5215,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5238,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736132</v>
+        <v>736292</v>
       </c>
       <c r="R46" t="n">
-        <v>7412974</v>
+        <v>7412983</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5274,11 +5279,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786904</v>
+        <v>122786896</v>
       </c>
       <c r="B47" t="n">
-        <v>57589</v>
+        <v>57494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5317,20 +5317,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736358</v>
+        <v>736223</v>
       </c>
       <c r="R47" t="n">
-        <v>7413327</v>
+        <v>7413089</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786888</v>
+        <v>122786923</v>
       </c>
       <c r="B48" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,38 +5423,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736358</v>
+        <v>736316</v>
       </c>
       <c r="R48" t="n">
-        <v>7413327</v>
+        <v>7413295</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5487,11 +5483,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5518,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786919</v>
+        <v>122786888</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5534,34 +5525,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736372</v>
+        <v>736358</v>
       </c>
       <c r="R49" t="n">
-        <v>7413070</v>
+        <v>7413327</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5594,6 +5589,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5620,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786874</v>
+        <v>122786920</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5636,21 +5636,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736381</v>
+        <v>736393</v>
       </c>
       <c r="R50" t="n">
-        <v>7413321</v>
+        <v>7413048</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5696,11 +5696,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5727,10 +5722,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786872</v>
+        <v>122786919</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,21 +5738,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5767,10 +5762,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736447</v>
+        <v>736372</v>
       </c>
       <c r="R51" t="n">
-        <v>7413232</v>
+        <v>7413070</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5803,11 +5798,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5834,7 +5824,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786923</v>
+        <v>122786922</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -5874,10 +5864,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736316</v>
+        <v>736463</v>
       </c>
       <c r="R52" t="n">
-        <v>7413295</v>
+        <v>7413234</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5936,10 +5926,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786920</v>
+        <v>122786904</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>57589</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,25 +5938,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5976,10 +5966,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736393</v>
+        <v>736358</v>
       </c>
       <c r="R53" t="n">
-        <v>7413048</v>
+        <v>7413327</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6038,10 +6028,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786922</v>
+        <v>122786871</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6054,21 +6044,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6078,10 +6068,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736463</v>
+        <v>736468</v>
       </c>
       <c r="R54" t="n">
-        <v>7413234</v>
+        <v>7413177</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6114,6 +6104,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6140,10 +6135,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786873</v>
+        <v>122786921</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6156,21 +6151,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6180,10 +6175,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736260</v>
+        <v>736417</v>
       </c>
       <c r="R55" t="n">
-        <v>7413219</v>
+        <v>7413130</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6216,11 +6211,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6247,7 +6237,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786871</v>
+        <v>122786874</v>
       </c>
       <c r="B56" t="n">
         <v>57478</v>
@@ -6287,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736468</v>
+        <v>736381</v>
       </c>
       <c r="R56" t="n">
-        <v>7413177</v>
+        <v>7413321</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6327,7 +6317,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Över 20 ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6465,10 +6455,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786921</v>
+        <v>122786872</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6481,21 +6471,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6505,10 +6495,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736417</v>
+        <v>736447</v>
       </c>
       <c r="R58" t="n">
-        <v>7413130</v>
+        <v>7413232</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6541,6 +6531,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6567,10 +6562,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786896</v>
+        <v>122786873</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6583,16 +6578,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6607,10 +6602,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736223</v>
+        <v>736260</v>
       </c>
       <c r="R59" t="n">
-        <v>7413089</v>
+        <v>7413219</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6643,6 +6638,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R60" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R61" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692891</v>
+        <v>122692864</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736029</v>
+        <v>736292</v>
       </c>
       <c r="R2" t="n">
-        <v>7413135</v>
+        <v>7412983</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692865</v>
+        <v>122692899</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736116</v>
+        <v>736253</v>
       </c>
       <c r="R3" t="n">
-        <v>7412997</v>
+        <v>7413096</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -982,7 +982,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692895</v>
+        <v>122692903</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736222</v>
+        <v>736135</v>
       </c>
       <c r="R5" t="n">
-        <v>7413197</v>
+        <v>7412970</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692890</v>
+        <v>122692900</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736078</v>
+        <v>736268</v>
       </c>
       <c r="R6" t="n">
-        <v>7413098</v>
+        <v>7413074</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692896</v>
+        <v>122692850</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736227</v>
+        <v>736028</v>
       </c>
       <c r="R7" t="n">
-        <v>7413172</v>
+        <v>7413218</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1288,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692888</v>
+        <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736141</v>
+        <v>736167</v>
       </c>
       <c r="R8" t="n">
-        <v>7413344</v>
+        <v>7413243</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1366,13 +1366,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1391,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692914</v>
+        <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1403,25 +1407,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,7 +1438,7 @@
         <v>736141</v>
       </c>
       <c r="R9" t="n">
-        <v>7413319</v>
+        <v>7413297</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1475,7 +1479,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692861</v>
+        <v>122692887</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1506,25 +1509,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736142</v>
+        <v>735969</v>
       </c>
       <c r="R10" t="n">
-        <v>7413297</v>
+        <v>7413433</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1578,6 +1581,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1699,7 +1703,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692903</v>
+        <v>122692895</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1739,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736135</v>
+        <v>736222</v>
       </c>
       <c r="R12" t="n">
-        <v>7412970</v>
+        <v>7413197</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1801,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692913</v>
+        <v>122692868</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1817,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736262</v>
+        <v>736267</v>
       </c>
       <c r="R13" t="n">
-        <v>7413022</v>
+        <v>7413160</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1879,13 +1883,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1904,10 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692908</v>
+        <v>122692865</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1924,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736202</v>
+        <v>736116</v>
       </c>
       <c r="R14" t="n">
-        <v>7413250</v>
+        <v>7412997</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,11 +1988,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,7 +2014,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692901</v>
+        <v>122692897</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2051,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736256</v>
+        <v>736248</v>
       </c>
       <c r="R15" t="n">
-        <v>7413074</v>
+        <v>7413169</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,7 +2116,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692916</v>
+        <v>122692889</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2153,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736092</v>
+        <v>736006</v>
       </c>
       <c r="R16" t="n">
-        <v>7413264</v>
+        <v>7413410</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2216,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692886</v>
+        <v>122692901</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2250,19 +2253,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736116</v>
+        <v>736256</v>
       </c>
       <c r="R17" t="n">
-        <v>7412995</v>
+        <v>7413074</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2303,7 +2303,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2322,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692868</v>
+        <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736267</v>
+        <v>735946</v>
       </c>
       <c r="R18" t="n">
-        <v>7413160</v>
+        <v>7413485</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2402,7 +2401,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hackspår på torrträd</t>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692859</v>
+        <v>122692866</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>57631</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2440,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736141</v>
+        <v>736167</v>
       </c>
       <c r="R19" t="n">
-        <v>7413297</v>
+        <v>7413025</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2634,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692855</v>
+        <v>122692893</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736124</v>
+        <v>735982</v>
       </c>
       <c r="R21" t="n">
-        <v>7412945</v>
+        <v>7413229</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2736,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692876</v>
+        <v>122692856</v>
       </c>
       <c r="B22" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,20 +2747,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2776,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736253</v>
+        <v>736114</v>
       </c>
       <c r="R22" t="n">
-        <v>7413052</v>
+        <v>7412934</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2838,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692863</v>
+        <v>122692908</v>
       </c>
       <c r="B23" t="n">
         <v>56688</v>
@@ -2878,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736167</v>
+        <v>736202</v>
       </c>
       <c r="R23" t="n">
-        <v>7413243</v>
+        <v>7413250</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2918,7 +2917,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spår i snön</t>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2945,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692900</v>
+        <v>122692853</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2985,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736268</v>
+        <v>736120</v>
       </c>
       <c r="R24" t="n">
-        <v>7413074</v>
+        <v>7412935</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3047,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692897</v>
+        <v>122692890</v>
       </c>
       <c r="B25" t="n">
         <v>78766</v>
@@ -3087,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736248</v>
+        <v>736078</v>
       </c>
       <c r="R25" t="n">
-        <v>7413169</v>
+        <v>7413098</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3149,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692851</v>
+        <v>122692914</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3189,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736115</v>
+        <v>736141</v>
       </c>
       <c r="R26" t="n">
-        <v>7412928</v>
+        <v>7413319</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3233,6 +3232,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692856</v>
+        <v>122692867</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736114</v>
+        <v>736165</v>
       </c>
       <c r="R27" t="n">
-        <v>7412934</v>
+        <v>7413161</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692905</v>
+        <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3467,25 +3467,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736175</v>
+        <v>736132</v>
       </c>
       <c r="R29" t="n">
-        <v>7413127</v>
+        <v>7412974</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3531,6 +3531,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3557,7 +3562,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692904</v>
+        <v>122692915</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3597,10 +3602,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736171</v>
+        <v>736095</v>
       </c>
       <c r="R30" t="n">
-        <v>7412886</v>
+        <v>7413383</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3641,6 +3646,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3659,10 +3665,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692867</v>
+        <v>122692886</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3675,34 +3681,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736165</v>
+        <v>736116</v>
       </c>
       <c r="R31" t="n">
-        <v>7413161</v>
+        <v>7412995</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3743,6 +3752,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3771,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692877</v>
+        <v>122692861</v>
       </c>
       <c r="B32" t="n">
-        <v>57627</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3773,25 +3783,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103022</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736170</v>
+        <v>736142</v>
       </c>
       <c r="R32" t="n">
-        <v>7413160</v>
+        <v>7413297</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3863,10 +3873,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692915</v>
+        <v>122692851</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3879,21 +3889,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736095</v>
+        <v>736115</v>
       </c>
       <c r="R33" t="n">
-        <v>7413383</v>
+        <v>7412928</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3947,7 +3957,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3966,10 +3975,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692860</v>
+        <v>122692874</v>
       </c>
       <c r="B34" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3978,25 +3987,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4006,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736132</v>
+        <v>736203</v>
       </c>
       <c r="R34" t="n">
-        <v>7412974</v>
+        <v>7412940</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4044,17 +4053,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4073,10 +4078,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692850</v>
+        <v>122692877</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57627</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4089,21 +4094,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4113,10 +4118,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736028</v>
+        <v>736170</v>
       </c>
       <c r="R35" t="n">
-        <v>7413218</v>
+        <v>7413160</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4175,7 +4180,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692893</v>
+        <v>122692892</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4218,7 +4223,7 @@
         <v>735982</v>
       </c>
       <c r="R36" t="n">
-        <v>7413229</v>
+        <v>7413172</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4277,7 +4282,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692892</v>
+        <v>122692904</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4317,10 +4322,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735982</v>
+        <v>736171</v>
       </c>
       <c r="R37" t="n">
-        <v>7413172</v>
+        <v>7412886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4379,7 +4384,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692899</v>
+        <v>122692913</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4419,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736253</v>
+        <v>736262</v>
       </c>
       <c r="R38" t="n">
-        <v>7413096</v>
+        <v>7413022</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4463,6 +4468,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692866</v>
+        <v>122692891</v>
       </c>
       <c r="B39" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4497,21 +4503,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,10 +4527,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736167</v>
+        <v>736029</v>
       </c>
       <c r="R39" t="n">
-        <v>7413025</v>
+        <v>7413135</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4583,10 +4589,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692874</v>
+        <v>122692902</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4599,21 +4605,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4623,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736203</v>
+        <v>736287</v>
       </c>
       <c r="R40" t="n">
-        <v>7412940</v>
+        <v>7412989</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4667,7 +4673,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4686,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692887</v>
+        <v>122692905</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -4726,10 +4731,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735969</v>
+        <v>736175</v>
       </c>
       <c r="R41" t="n">
-        <v>7413433</v>
+        <v>7413127</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4770,7 +4775,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4789,7 +4793,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692889</v>
+        <v>122692888</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -4829,10 +4833,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736006</v>
+        <v>736141</v>
       </c>
       <c r="R42" t="n">
-        <v>7413410</v>
+        <v>7413344</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4892,7 +4896,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692902</v>
+        <v>122692916</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -4932,10 +4936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736287</v>
+        <v>736092</v>
       </c>
       <c r="R43" t="n">
-        <v>7412989</v>
+        <v>7413264</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4976,6 +4980,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4994,7 +4999,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692853</v>
+        <v>122692855</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5034,10 +5039,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736120</v>
+        <v>736124</v>
       </c>
       <c r="R44" t="n">
-        <v>7412935</v>
+        <v>7412945</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5096,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692862</v>
+        <v>122692876</v>
       </c>
       <c r="B45" t="n">
-        <v>56688</v>
+        <v>57589</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5112,21 +5117,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5136,10 +5141,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>735946</v>
+        <v>736253</v>
       </c>
       <c r="R45" t="n">
-        <v>7413485</v>
+        <v>7413052</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5172,11 +5177,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5203,10 +5203,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692864</v>
+        <v>122692896</v>
       </c>
       <c r="B46" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5219,21 +5219,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736292</v>
+        <v>736227</v>
       </c>
       <c r="R46" t="n">
-        <v>7412983</v>
+        <v>7413172</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786896</v>
+        <v>122786874</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,16 +5321,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736223</v>
+        <v>736381</v>
       </c>
       <c r="R47" t="n">
-        <v>7413089</v>
+        <v>7413321</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5381,6 +5381,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5407,10 +5412,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786923</v>
+        <v>122786873</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5423,21 +5428,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5447,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736316</v>
+        <v>736260</v>
       </c>
       <c r="R48" t="n">
-        <v>7413295</v>
+        <v>7413219</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5483,6 +5488,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5509,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786888</v>
+        <v>122786871</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5525,38 +5535,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736358</v>
+        <v>736468</v>
       </c>
       <c r="R49" t="n">
-        <v>7413327</v>
+        <v>7413177</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5593,7 +5599,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5620,7 +5626,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786920</v>
+        <v>122786919</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -5660,10 +5666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736393</v>
+        <v>736372</v>
       </c>
       <c r="R50" t="n">
-        <v>7413048</v>
+        <v>7413070</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5722,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786919</v>
+        <v>122786887</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5734,38 +5740,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736372</v>
+        <v>736375</v>
       </c>
       <c r="R51" t="n">
-        <v>7413070</v>
+        <v>7413284</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5798,6 +5808,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5824,10 +5839,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786922</v>
+        <v>122786872</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5840,21 +5855,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5864,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736463</v>
+        <v>736447</v>
       </c>
       <c r="R52" t="n">
-        <v>7413234</v>
+        <v>7413232</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5900,6 +5915,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5926,10 +5946,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786904</v>
+        <v>122786888</v>
       </c>
       <c r="B53" t="n">
-        <v>57589</v>
+        <v>57631</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5938,28 +5958,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
@@ -6002,6 +6026,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6028,10 +6057,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786871</v>
+        <v>122786922</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6044,21 +6073,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6068,10 +6097,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736468</v>
+        <v>736463</v>
       </c>
       <c r="R54" t="n">
-        <v>7413177</v>
+        <v>7413234</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6104,11 +6133,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6135,7 +6159,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786921</v>
+        <v>122786920</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6175,10 +6199,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736417</v>
+        <v>736393</v>
       </c>
       <c r="R55" t="n">
-        <v>7413130</v>
+        <v>7413048</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6237,10 +6261,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786874</v>
+        <v>122786921</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6253,21 +6277,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6301,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736381</v>
+        <v>736417</v>
       </c>
       <c r="R56" t="n">
-        <v>7413321</v>
+        <v>7413130</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6313,11 +6337,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6344,10 +6363,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786887</v>
+        <v>122786923</v>
       </c>
       <c r="B57" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6356,42 +6375,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736375</v>
+        <v>736316</v>
       </c>
       <c r="R57" t="n">
-        <v>7413284</v>
+        <v>7413295</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6424,11 +6439,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6455,10 +6465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786872</v>
+        <v>122786896</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,16 +6481,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6495,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736447</v>
+        <v>736223</v>
       </c>
       <c r="R58" t="n">
-        <v>7413232</v>
+        <v>7413089</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6531,11 +6541,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6562,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786873</v>
+        <v>122786904</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6574,20 +6579,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6602,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736260</v>
+        <v>736358</v>
       </c>
       <c r="R59" t="n">
-        <v>7413219</v>
+        <v>7413327</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6638,11 +6643,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B60" t="n">
         <v>57494</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R60" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B61" t="n">
         <v>57494</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R61" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692864</v>
+        <v>122692899</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736292</v>
+        <v>736253</v>
       </c>
       <c r="R2" t="n">
-        <v>7412983</v>
+        <v>7413096</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692899</v>
+        <v>122692879</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +820,7 @@
         <v>736253</v>
       </c>
       <c r="R3" t="n">
-        <v>7413096</v>
+        <v>7413052</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,6 +861,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692879</v>
+        <v>122692903</v>
       </c>
       <c r="B4" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736253</v>
+        <v>736135</v>
       </c>
       <c r="R4" t="n">
-        <v>7413052</v>
+        <v>7412970</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +982,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692903</v>
+        <v>122692900</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736135</v>
+        <v>736268</v>
       </c>
       <c r="R5" t="n">
-        <v>7412970</v>
+        <v>7413074</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692900</v>
+        <v>122692864</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736268</v>
+        <v>736292</v>
       </c>
       <c r="R6" t="n">
-        <v>7413074</v>
+        <v>7412983</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692915</v>
+        <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3574,25 +3574,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736095</v>
+        <v>736142</v>
       </c>
       <c r="R30" t="n">
-        <v>7413383</v>
+        <v>7413297</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3646,7 +3646,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3665,7 +3664,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692886</v>
+        <v>122692915</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3699,19 +3698,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736116</v>
+        <v>736095</v>
       </c>
       <c r="R31" t="n">
-        <v>7412995</v>
+        <v>7413383</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3771,10 +3767,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692861</v>
+        <v>122692886</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3783,38 +3779,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736142</v>
+        <v>736116</v>
       </c>
       <c r="R32" t="n">
-        <v>7413297</v>
+        <v>7412995</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,6 +3854,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3975,10 +3975,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692874</v>
+        <v>122692877</v>
       </c>
       <c r="B34" t="n">
-        <v>78503</v>
+        <v>57627</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3991,21 +3991,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>103022</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736203</v>
+        <v>736170</v>
       </c>
       <c r="R34" t="n">
-        <v>7412940</v>
+        <v>7413160</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4059,7 +4059,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4078,10 +4077,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692877</v>
+        <v>122692874</v>
       </c>
       <c r="B35" t="n">
-        <v>57627</v>
+        <v>78503</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4094,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103022</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4118,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736170</v>
+        <v>736203</v>
       </c>
       <c r="R35" t="n">
-        <v>7413160</v>
+        <v>7412940</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4162,6 +4161,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786874</v>
+        <v>122786888</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57634</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,34 +5321,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736381</v>
+        <v>736358</v>
       </c>
       <c r="R47" t="n">
-        <v>7413321</v>
+        <v>7413327</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5385,7 +5389,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5412,10 +5416,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786873</v>
+        <v>122786920</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,21 +5432,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5452,10 +5456,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736260</v>
+        <v>736393</v>
       </c>
       <c r="R48" t="n">
-        <v>7413219</v>
+        <v>7413048</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5488,11 +5492,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5519,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786871</v>
+        <v>122786873</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5559,10 +5558,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736468</v>
+        <v>736260</v>
       </c>
       <c r="R49" t="n">
-        <v>7413177</v>
+        <v>7413219</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5599,7 +5598,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Över 20 ringhack</t>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5626,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786919</v>
+        <v>122786871</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5642,21 +5641,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5666,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736372</v>
+        <v>736468</v>
       </c>
       <c r="R50" t="n">
-        <v>7413070</v>
+        <v>7413177</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5702,6 +5701,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5728,10 +5732,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786887</v>
+        <v>122786896</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>57497</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5740,42 +5744,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736375</v>
+        <v>736223</v>
       </c>
       <c r="R51" t="n">
-        <v>7413284</v>
+        <v>7413089</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5808,11 +5808,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5839,10 +5834,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786872</v>
+        <v>122786887</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>56691</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5851,38 +5846,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736447</v>
+        <v>736375</v>
       </c>
       <c r="R52" t="n">
-        <v>7413232</v>
+        <v>7413284</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5919,7 +5918,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5946,10 +5945,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786888</v>
+        <v>122786874</v>
       </c>
       <c r="B53" t="n">
-        <v>57631</v>
+        <v>57481</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5962,38 +5961,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736358</v>
+        <v>736381</v>
       </c>
       <c r="R53" t="n">
-        <v>7413327</v>
+        <v>7413321</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6030,7 +6025,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6060,7 +6055,7 @@
         <v>122786922</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6159,10 +6154,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786920</v>
+        <v>122786904</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>57592</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6171,25 +6166,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6199,10 +6194,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736393</v>
+        <v>736358</v>
       </c>
       <c r="R55" t="n">
-        <v>7413048</v>
+        <v>7413327</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6261,10 +6256,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786921</v>
+        <v>122786923</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6301,10 +6296,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736417</v>
+        <v>736316</v>
       </c>
       <c r="R56" t="n">
-        <v>7413130</v>
+        <v>7413295</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6363,10 +6358,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786923</v>
+        <v>122786919</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736316</v>
+        <v>736372</v>
       </c>
       <c r="R57" t="n">
-        <v>7413295</v>
+        <v>7413070</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6465,10 +6460,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786896</v>
+        <v>122786921</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6481,21 +6476,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6505,10 +6500,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736223</v>
+        <v>736417</v>
       </c>
       <c r="R58" t="n">
-        <v>7413089</v>
+        <v>7413130</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6567,10 +6562,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786904</v>
+        <v>122786872</v>
       </c>
       <c r="B59" t="n">
-        <v>57589</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6579,20 +6574,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6607,10 +6602,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736358</v>
+        <v>736447</v>
       </c>
       <c r="R59" t="n">
-        <v>7413327</v>
+        <v>7413232</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6643,6 +6638,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6672,7 +6672,7 @@
         <v>122800283</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>122800284</v>
       </c>
       <c r="B61" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786888</v>
+        <v>122786923</v>
       </c>
       <c r="B47" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,38 +5321,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736358</v>
+        <v>736316</v>
       </c>
       <c r="R47" t="n">
-        <v>7413327</v>
+        <v>7413295</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5385,11 +5381,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5416,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786920</v>
+        <v>122786887</v>
       </c>
       <c r="B48" t="n">
-        <v>78769</v>
+        <v>56691</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,38 +5419,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736393</v>
+        <v>736375</v>
       </c>
       <c r="R48" t="n">
-        <v>7413048</v>
+        <v>7413284</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5492,6 +5487,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5625,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786871</v>
+        <v>122786919</v>
       </c>
       <c r="B50" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736468</v>
+        <v>736372</v>
       </c>
       <c r="R50" t="n">
-        <v>7413177</v>
+        <v>7413070</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5701,11 +5701,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5732,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786896</v>
+        <v>122786920</v>
       </c>
       <c r="B51" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5748,21 +5743,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5772,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736223</v>
+        <v>736393</v>
       </c>
       <c r="R51" t="n">
-        <v>7413089</v>
+        <v>7413048</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5834,10 +5829,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786887</v>
+        <v>122786888</v>
       </c>
       <c r="B52" t="n">
-        <v>56691</v>
+        <v>57634</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,42 +5841,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736375</v>
+        <v>736358</v>
       </c>
       <c r="R52" t="n">
-        <v>7413284</v>
+        <v>7413327</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5918,7 +5913,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5945,10 +5940,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786874</v>
+        <v>122786904</v>
       </c>
       <c r="B53" t="n">
-        <v>57481</v>
+        <v>57592</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5957,20 +5952,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5985,10 +5980,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736381</v>
+        <v>736358</v>
       </c>
       <c r="R53" t="n">
-        <v>7413321</v>
+        <v>7413327</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6021,11 +6016,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6052,10 +6042,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786922</v>
+        <v>122786874</v>
       </c>
       <c r="B54" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6068,21 +6058,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6092,10 +6082,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736463</v>
+        <v>736381</v>
       </c>
       <c r="R54" t="n">
-        <v>7413234</v>
+        <v>7413321</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6128,6 +6118,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6154,10 +6149,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786904</v>
+        <v>122786896</v>
       </c>
       <c r="B55" t="n">
-        <v>57592</v>
+        <v>57497</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6166,20 +6161,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6194,10 +6189,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736358</v>
+        <v>736223</v>
       </c>
       <c r="R55" t="n">
-        <v>7413327</v>
+        <v>7413089</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6256,10 +6251,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786923</v>
+        <v>122786872</v>
       </c>
       <c r="B56" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6272,21 +6267,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6296,10 +6291,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736316</v>
+        <v>736447</v>
       </c>
       <c r="R56" t="n">
-        <v>7413295</v>
+        <v>7413232</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6332,6 +6327,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6358,10 +6358,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786919</v>
+        <v>122786871</v>
       </c>
       <c r="B57" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6374,21 +6374,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736372</v>
+        <v>736468</v>
       </c>
       <c r="R57" t="n">
-        <v>7413070</v>
+        <v>7413177</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6434,6 +6434,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6463,7 +6468,7 @@
         <v>122786921</v>
       </c>
       <c r="B58" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6562,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786872</v>
+        <v>122786922</v>
       </c>
       <c r="B59" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6578,21 +6583,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6602,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736447</v>
+        <v>736463</v>
       </c>
       <c r="R59" t="n">
-        <v>7413232</v>
+        <v>7413234</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6638,11 +6643,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -5727,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786920</v>
+        <v>122786888</v>
       </c>
       <c r="B51" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,34 +5743,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736393</v>
+        <v>736358</v>
       </c>
       <c r="R51" t="n">
-        <v>7413048</v>
+        <v>7413327</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5803,6 +5807,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5829,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786888</v>
+        <v>122786920</v>
       </c>
       <c r="B52" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,38 +5854,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736358</v>
+        <v>736393</v>
       </c>
       <c r="R52" t="n">
-        <v>7413327</v>
+        <v>7413048</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5909,11 +5914,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786923</v>
+        <v>122786872</v>
       </c>
       <c r="B47" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736316</v>
+        <v>736447</v>
       </c>
       <c r="R47" t="n">
-        <v>7413295</v>
+        <v>7413232</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5381,6 +5381,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5407,10 +5412,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786887</v>
+        <v>122786871</v>
       </c>
       <c r="B48" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5419,42 +5424,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736375</v>
+        <v>736468</v>
       </c>
       <c r="R48" t="n">
-        <v>7413284</v>
+        <v>7413177</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5491,7 +5492,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5518,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786873</v>
+        <v>122786921</v>
       </c>
       <c r="B49" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5534,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5558,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736260</v>
+        <v>736417</v>
       </c>
       <c r="R49" t="n">
-        <v>7413219</v>
+        <v>7413130</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5594,11 +5595,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5625,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786919</v>
+        <v>122786887</v>
       </c>
       <c r="B50" t="n">
-        <v>78771</v>
+        <v>56691</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5637,38 +5633,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736372</v>
+        <v>736375</v>
       </c>
       <c r="R50" t="n">
-        <v>7413070</v>
+        <v>7413284</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5701,6 +5701,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5727,10 +5732,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786888</v>
+        <v>122786920</v>
       </c>
       <c r="B51" t="n">
-        <v>57634</v>
+        <v>78772</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,38 +5748,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736358</v>
+        <v>736393</v>
       </c>
       <c r="R51" t="n">
-        <v>7413327</v>
+        <v>7413048</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5807,11 +5808,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Par</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5838,10 +5834,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786920</v>
+        <v>122786896</v>
       </c>
       <c r="B52" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5854,21 +5850,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5874,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736393</v>
+        <v>736223</v>
       </c>
       <c r="R52" t="n">
-        <v>7413048</v>
+        <v>7413089</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5940,10 +5936,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786904</v>
+        <v>122786919</v>
       </c>
       <c r="B53" t="n">
-        <v>57592</v>
+        <v>78772</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5952,25 +5948,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5980,10 +5976,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736358</v>
+        <v>736372</v>
       </c>
       <c r="R53" t="n">
-        <v>7413327</v>
+        <v>7413070</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6149,10 +6145,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786896</v>
+        <v>122786888</v>
       </c>
       <c r="B55" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,34 +6161,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736223</v>
+        <v>736358</v>
       </c>
       <c r="R55" t="n">
-        <v>7413089</v>
+        <v>7413327</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6225,6 +6225,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6251,7 +6256,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786872</v>
+        <v>122786873</v>
       </c>
       <c r="B56" t="n">
         <v>57481</v>
@@ -6291,10 +6296,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736447</v>
+        <v>736260</v>
       </c>
       <c r="R56" t="n">
-        <v>7413232</v>
+        <v>7413219</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6331,7 +6336,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6358,10 +6363,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786871</v>
+        <v>122786923</v>
       </c>
       <c r="B57" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6374,21 +6379,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736468</v>
+        <v>736316</v>
       </c>
       <c r="R57" t="n">
-        <v>7413177</v>
+        <v>7413295</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6434,11 +6439,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6465,10 +6465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786921</v>
+        <v>122786922</v>
       </c>
       <c r="B58" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736417</v>
+        <v>736463</v>
       </c>
       <c r="R58" t="n">
-        <v>7413130</v>
+        <v>7413234</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6567,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786922</v>
+        <v>122786904</v>
       </c>
       <c r="B59" t="n">
-        <v>78771</v>
+        <v>57592</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6579,25 +6579,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736463</v>
+        <v>736358</v>
       </c>
       <c r="R59" t="n">
-        <v>7413234</v>
+        <v>7413327</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B60" t="n">
         <v>57497</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R60" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B61" t="n">
         <v>57497</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R61" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -5305,10 +5305,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786872</v>
+        <v>122786920</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736447</v>
+        <v>736393</v>
       </c>
       <c r="R47" t="n">
-        <v>7413232</v>
+        <v>7413048</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5381,11 +5381,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5412,10 +5407,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786871</v>
+        <v>122786923</v>
       </c>
       <c r="B48" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,21 +5423,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736468</v>
+        <v>736316</v>
       </c>
       <c r="R48" t="n">
-        <v>7413177</v>
+        <v>7413295</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5488,11 +5483,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5519,10 +5509,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786921</v>
+        <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>56691</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5531,38 +5521,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736417</v>
+        <v>736375</v>
       </c>
       <c r="R49" t="n">
-        <v>7413130</v>
+        <v>7413284</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5595,6 +5589,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5621,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786887</v>
+        <v>122786919</v>
       </c>
       <c r="B50" t="n">
-        <v>56691</v>
+        <v>78775</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5633,42 +5632,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736375</v>
+        <v>736372</v>
       </c>
       <c r="R50" t="n">
-        <v>7413284</v>
+        <v>7413070</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5701,11 +5696,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5732,10 +5722,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786920</v>
+        <v>122786896</v>
       </c>
       <c r="B51" t="n">
-        <v>78772</v>
+        <v>57497</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5748,21 +5738,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5772,10 +5762,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736393</v>
+        <v>736223</v>
       </c>
       <c r="R51" t="n">
-        <v>7413048</v>
+        <v>7413089</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5834,10 +5824,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786896</v>
+        <v>122786904</v>
       </c>
       <c r="B52" t="n">
-        <v>57497</v>
+        <v>57592</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,20 +5836,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5874,10 +5864,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736223</v>
+        <v>736358</v>
       </c>
       <c r="R52" t="n">
-        <v>7413089</v>
+        <v>7413327</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5936,10 +5926,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786919</v>
+        <v>122786921</v>
       </c>
       <c r="B53" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5976,10 +5966,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736372</v>
+        <v>736417</v>
       </c>
       <c r="R53" t="n">
-        <v>7413070</v>
+        <v>7413130</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6038,10 +6028,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786874</v>
+        <v>122786922</v>
       </c>
       <c r="B54" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6054,21 +6044,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6078,10 +6068,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736381</v>
+        <v>736463</v>
       </c>
       <c r="R54" t="n">
-        <v>7413321</v>
+        <v>7413234</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6114,11 +6104,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6145,10 +6130,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786888</v>
+        <v>122786872</v>
       </c>
       <c r="B55" t="n">
-        <v>57634</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6161,38 +6146,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736358</v>
+        <v>736447</v>
       </c>
       <c r="R55" t="n">
-        <v>7413327</v>
+        <v>7413232</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6229,7 +6210,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Par</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6256,10 +6237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786873</v>
+        <v>122786888</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6272,34 +6253,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736260</v>
+        <v>736358</v>
       </c>
       <c r="R56" t="n">
-        <v>7413219</v>
+        <v>7413327</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6336,7 +6321,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Flera rader ringhack</t>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6363,10 +6348,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786923</v>
+        <v>122786874</v>
       </c>
       <c r="B57" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6379,21 +6364,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6403,10 +6388,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736316</v>
+        <v>736381</v>
       </c>
       <c r="R57" t="n">
-        <v>7413295</v>
+        <v>7413321</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6439,6 +6424,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6465,10 +6455,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786922</v>
+        <v>122786871</v>
       </c>
       <c r="B58" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6481,21 +6471,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6505,10 +6495,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736463</v>
+        <v>736468</v>
       </c>
       <c r="R58" t="n">
-        <v>7413234</v>
+        <v>7413177</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6541,6 +6531,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6567,10 +6562,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786904</v>
+        <v>122786873</v>
       </c>
       <c r="B59" t="n">
-        <v>57592</v>
+        <v>57481</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6579,20 +6574,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6607,10 +6602,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736358</v>
+        <v>736260</v>
       </c>
       <c r="R59" t="n">
-        <v>7413327</v>
+        <v>7413219</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6643,6 +6638,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6669,7 +6669,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800284</v>
+        <v>122800283</v>
       </c>
       <c r="B60" t="n">
         <v>57497</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736110</v>
+        <v>736133</v>
       </c>
       <c r="R60" t="n">
-        <v>7413053</v>
+        <v>7412935</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800283</v>
+        <v>122800284</v>
       </c>
       <c r="B61" t="n">
         <v>57497</v>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736133</v>
+        <v>736110</v>
       </c>
       <c r="R61" t="n">
-        <v>7412935</v>
+        <v>7413053</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>122692863</v>
       </c>
       <c r="B8" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>122692859</v>
       </c>
       <c r="B9" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>122692862</v>
       </c>
       <c r="B18" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>122692908</v>
       </c>
       <c r="B23" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>122692860</v>
       </c>
       <c r="B29" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>122692861</v>
       </c>
       <c r="B30" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>122786887</v>
       </c>
       <c r="B49" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122692899</v>
+        <v>122692906</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736253</v>
+        <v>736295</v>
       </c>
       <c r="R2" t="n">
-        <v>7413096</v>
+        <v>7412988</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,50 +773,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122692879</v>
+        <v>122692886</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736253</v>
+        <v>736116</v>
       </c>
       <c r="R3" t="n">
-        <v>7413052</v>
+        <v>7412995</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,19 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122692903</v>
+        <v>122692887</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -920,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736135</v>
+        <v>735969</v>
       </c>
       <c r="R4" t="n">
-        <v>7412970</v>
+        <v>7413433</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,6 +953,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,19 +972,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122692900</v>
+        <v>122692888</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1022,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736268</v>
+        <v>736141</v>
       </c>
       <c r="R5" t="n">
-        <v>7413074</v>
+        <v>7413344</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1066,6 +1051,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,37 +1070,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122692864</v>
+        <v>122692889</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1105,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736292</v>
+        <v>736006</v>
       </c>
       <c r="R6" t="n">
-        <v>7412983</v>
+        <v>7413410</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1168,6 +1149,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,37 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122692850</v>
+        <v>122692890</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736028</v>
+        <v>736078</v>
       </c>
       <c r="R7" t="n">
-        <v>7413218</v>
+        <v>7413098</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1288,32 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122692863</v>
+        <v>122692891</v>
       </c>
       <c r="B8" t="n">
-        <v>57092</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1323,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736167</v>
+        <v>736029</v>
       </c>
       <c r="R8" t="n">
-        <v>7413243</v>
+        <v>7413135</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1359,11 +1336,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1390,32 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122692859</v>
+        <v>122692892</v>
       </c>
       <c r="B9" t="n">
-        <v>57092</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736141</v>
+        <v>735982</v>
       </c>
       <c r="R9" t="n">
-        <v>7413297</v>
+        <v>7413172</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1487,19 +1459,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122692887</v>
+        <v>122692893</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1527,10 +1494,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735969</v>
+        <v>735982</v>
       </c>
       <c r="R10" t="n">
-        <v>7413433</v>
+        <v>7413229</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1571,7 +1538,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,37 +1556,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122692880</v>
+        <v>122692895</v>
       </c>
       <c r="B11" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1630,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736205</v>
+        <v>736222</v>
       </c>
       <c r="R11" t="n">
-        <v>7412943</v>
+        <v>7413197</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,7 +1635,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1693,19 +1653,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122692895</v>
+        <v>122692896</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1733,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736222</v>
+        <v>736227</v>
       </c>
       <c r="R12" t="n">
-        <v>7413197</v>
+        <v>7413172</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1795,37 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122692868</v>
+        <v>122692897</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1835,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736267</v>
+        <v>736248</v>
       </c>
       <c r="R13" t="n">
-        <v>7413160</v>
+        <v>7413169</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,11 +1821,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår på torrträd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,37 +1847,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122692865</v>
+        <v>122692899</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736116</v>
+        <v>736253</v>
       </c>
       <c r="R14" t="n">
-        <v>7412997</v>
+        <v>7413096</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2004,19 +1944,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122692897</v>
+        <v>122692900</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2044,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736248</v>
+        <v>736268</v>
       </c>
       <c r="R15" t="n">
-        <v>7413169</v>
+        <v>7413074</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2106,19 +2041,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122692889</v>
+        <v>122692901</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2146,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736006</v>
+        <v>736256</v>
       </c>
       <c r="R16" t="n">
-        <v>7413410</v>
+        <v>7413074</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2190,7 +2120,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,19 +2138,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122692901</v>
+        <v>122692902</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2249,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736256</v>
+        <v>736287</v>
       </c>
       <c r="R17" t="n">
-        <v>7413074</v>
+        <v>7412989</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2311,32 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122692862</v>
+        <v>122692903</v>
       </c>
       <c r="B18" t="n">
-        <v>57092</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2346,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735946</v>
+        <v>736135</v>
       </c>
       <c r="R18" t="n">
-        <v>7413485</v>
+        <v>7412970</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2382,11 +2306,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,37 +2332,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122692866</v>
+        <v>122692904</v>
       </c>
       <c r="B19" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2367,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736167</v>
+        <v>736171</v>
       </c>
       <c r="R19" t="n">
-        <v>7413025</v>
+        <v>7412886</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2515,37 +2429,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122692906</v>
+        <v>122692905</v>
       </c>
       <c r="B20" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2464,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736295</v>
+        <v>736175</v>
       </c>
       <c r="R20" t="n">
-        <v>7412988</v>
+        <v>7413127</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2599,7 +2508,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2618,19 +2526,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122692893</v>
+        <v>122692913</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2658,10 +2561,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735982</v>
+        <v>736262</v>
       </c>
       <c r="R21" t="n">
-        <v>7413229</v>
+        <v>7413022</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2702,6 +2605,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,37 +2624,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122692856</v>
+        <v>122692914</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736114</v>
+        <v>736141</v>
       </c>
       <c r="R22" t="n">
-        <v>7412934</v>
+        <v>7413319</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2804,6 +2703,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2822,32 +2722,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122692908</v>
+        <v>122692915</v>
       </c>
       <c r="B23" t="n">
-        <v>57092</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736202</v>
+        <v>736095</v>
       </c>
       <c r="R23" t="n">
-        <v>7413250</v>
+        <v>7413383</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2895,17 +2795,13 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2924,37 +2820,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122692853</v>
+        <v>122692916</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2855,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736120</v>
+        <v>736092</v>
       </c>
       <c r="R24" t="n">
-        <v>7412935</v>
+        <v>7413264</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3008,6 +2899,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3026,19 +2918,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122692890</v>
+        <v>122786919</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3066,13 +2953,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736078</v>
+        <v>736372</v>
       </c>
       <c r="R25" t="n">
-        <v>7413098</v>
+        <v>7413070</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3096,12 +2983,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3128,19 +3015,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122692914</v>
+        <v>122786920</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3168,13 +3050,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736141</v>
+        <v>736393</v>
       </c>
       <c r="R26" t="n">
-        <v>7413319</v>
+        <v>7413048</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3198,12 +3080,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3212,7 +3094,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3231,37 +3112,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122692867</v>
+        <v>122786921</v>
       </c>
       <c r="B27" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3271,13 +3147,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736165</v>
+        <v>736417</v>
       </c>
       <c r="R27" t="n">
-        <v>7413161</v>
+        <v>7413130</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3301,12 +3177,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3333,37 +3209,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122692852</v>
+        <v>122786922</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3373,13 +3244,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736126</v>
+        <v>736463</v>
       </c>
       <c r="R28" t="n">
-        <v>7412904</v>
+        <v>7413234</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3403,12 +3274,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3435,32 +3306,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122692860</v>
+        <v>122786923</v>
       </c>
       <c r="B29" t="n">
-        <v>57092</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,13 +3341,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736132</v>
+        <v>736316</v>
       </c>
       <c r="R29" t="n">
-        <v>7412974</v>
+        <v>7413295</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3500,17 +3371,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Tjädertall</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3537,32 +3403,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122692861</v>
+        <v>122692879</v>
       </c>
       <c r="B30" t="n">
-        <v>57092</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3572,10 +3438,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736142</v>
+        <v>736253</v>
       </c>
       <c r="R30" t="n">
-        <v>7413297</v>
+        <v>7413052</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3616,6 +3482,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3634,15 +3501,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122692915</v>
+        <v>122692880</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,21 +3512,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3674,10 +3536,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736095</v>
+        <v>736205</v>
       </c>
       <c r="R31" t="n">
-        <v>7413383</v>
+        <v>7412943</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3737,53 +3599,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122692886</v>
+        <v>122692868</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736116</v>
+        <v>736267</v>
       </c>
       <c r="R32" t="n">
-        <v>7412995</v>
+        <v>7413160</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3818,13 +3672,17 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår på torrträd</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3843,32 +3701,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122692851</v>
+        <v>122786896</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3883,13 +3736,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736115</v>
+        <v>736223</v>
       </c>
       <c r="R33" t="n">
-        <v>7412928</v>
+        <v>7413089</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3913,12 +3766,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3945,37 +3798,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122692877</v>
+        <v>122800283</v>
       </c>
       <c r="B34" t="n">
-        <v>57627</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103022</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3985,13 +3833,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736170</v>
+        <v>736133</v>
       </c>
       <c r="R34" t="n">
-        <v>7413160</v>
+        <v>7412935</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4015,12 +3863,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4047,37 +3895,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122692874</v>
+        <v>122800284</v>
       </c>
       <c r="B35" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4087,13 +3930,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736203</v>
+        <v>736110</v>
       </c>
       <c r="R35" t="n">
-        <v>7412940</v>
+        <v>7413053</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4117,12 +3960,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4131,7 +3974,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4150,15 +3992,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122692892</v>
+        <v>122692850</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,21 +4003,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4190,10 +4027,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>735982</v>
+        <v>736028</v>
       </c>
       <c r="R36" t="n">
-        <v>7413172</v>
+        <v>7413218</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4252,15 +4089,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122692904</v>
+        <v>122692851</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4268,21 +4100,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4292,10 +4124,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736171</v>
+        <v>736115</v>
       </c>
       <c r="R37" t="n">
-        <v>7412886</v>
+        <v>7412928</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4354,15 +4186,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122692913</v>
+        <v>122692852</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4370,21 +4197,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4394,10 +4221,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736262</v>
+        <v>736126</v>
       </c>
       <c r="R38" t="n">
-        <v>7413022</v>
+        <v>7412904</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4438,7 +4265,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4457,15 +4283,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122692891</v>
+        <v>122692853</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,21 +4294,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4497,10 +4318,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736029</v>
+        <v>736120</v>
       </c>
       <c r="R39" t="n">
-        <v>7413135</v>
+        <v>7412935</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4559,15 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122692902</v>
+        <v>122692855</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,21 +4391,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4599,10 +4415,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736287</v>
+        <v>736124</v>
       </c>
       <c r="R40" t="n">
-        <v>7412989</v>
+        <v>7412945</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4661,15 +4477,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122692905</v>
+        <v>122692856</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4677,21 +4488,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4701,10 +4512,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736175</v>
+        <v>736114</v>
       </c>
       <c r="R41" t="n">
-        <v>7413127</v>
+        <v>7412934</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4763,15 +4574,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122692888</v>
+        <v>122786871</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4779,21 +4585,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4803,13 +4609,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736141</v>
+        <v>736468</v>
       </c>
       <c r="R42" t="n">
-        <v>7413344</v>
+        <v>7413177</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4833,12 +4639,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Över 20 ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4847,7 +4658,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4866,15 +4676,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122692916</v>
+        <v>122786872</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4882,21 +4687,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,13 +4711,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736092</v>
+        <v>736447</v>
       </c>
       <c r="R43" t="n">
-        <v>7413264</v>
+        <v>7413232</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4936,12 +4741,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,7 +4760,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4969,15 +4778,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122692855</v>
+        <v>122786873</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5009,13 +4813,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736124</v>
+        <v>736260</v>
       </c>
       <c r="R44" t="n">
-        <v>7412945</v>
+        <v>7413219</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5039,12 +4843,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Flera rader ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5071,32 +4880,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122692876</v>
+        <v>122786874</v>
       </c>
       <c r="B45" t="n">
-        <v>57589</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5111,13 +4915,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736253</v>
+        <v>736381</v>
       </c>
       <c r="R45" t="n">
-        <v>7413052</v>
+        <v>7413321</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5141,12 +4945,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,37 +4982,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122692896</v>
+        <v>122692859</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5017,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736227</v>
+        <v>736141</v>
       </c>
       <c r="R46" t="n">
-        <v>7413172</v>
+        <v>7413297</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5275,37 +5079,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122786920</v>
+        <v>122692860</v>
       </c>
       <c r="B47" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,13 +5114,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736393</v>
+        <v>736132</v>
       </c>
       <c r="R47" t="n">
-        <v>7413048</v>
+        <v>7412974</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5345,12 +5144,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,37 +5181,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122786923</v>
+        <v>122692861</v>
       </c>
       <c r="B48" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5417,13 +5216,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736316</v>
+        <v>736142</v>
       </c>
       <c r="R48" t="n">
-        <v>7413295</v>
+        <v>7413297</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5447,12 +5246,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5479,10 +5278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122786887</v>
+        <v>122692862</v>
       </c>
       <c r="B49" t="n">
-        <v>57092</v>
+        <v>57141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5508,23 +5307,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736375</v>
+        <v>735946</v>
       </c>
       <c r="R49" t="n">
-        <v>7413284</v>
+        <v>7413485</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5548,17 +5343,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5585,37 +5380,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122786919</v>
+        <v>122692863</v>
       </c>
       <c r="B50" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5625,13 +5415,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736372</v>
+        <v>736167</v>
       </c>
       <c r="R50" t="n">
-        <v>7413070</v>
+        <v>7413243</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5655,12 +5445,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5687,37 +5482,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122786896</v>
+        <v>122692908</v>
       </c>
       <c r="B51" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5727,13 +5517,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736223</v>
+        <v>736202</v>
       </c>
       <c r="R51" t="n">
-        <v>7413089</v>
+        <v>7413250</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5757,12 +5547,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Tjädertall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5789,15 +5584,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122786904</v>
+        <v>122786887</v>
       </c>
       <c r="B52" t="n">
-        <v>57592</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5805,34 +5595,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736358</v>
+        <v>736375</v>
       </c>
       <c r="R52" t="n">
-        <v>7413327</v>
+        <v>7413284</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5865,6 +5659,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5891,15 +5690,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122786921</v>
+        <v>122692864</v>
       </c>
       <c r="B53" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,21 +5701,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5931,13 +5725,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736417</v>
+        <v>736292</v>
       </c>
       <c r="R53" t="n">
-        <v>7413130</v>
+        <v>7412983</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5961,12 +5755,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5993,15 +5787,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122786922</v>
+        <v>122692865</v>
       </c>
       <c r="B54" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6009,21 +5798,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6033,13 +5822,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736463</v>
+        <v>736116</v>
       </c>
       <c r="R54" t="n">
-        <v>7413234</v>
+        <v>7412997</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6063,12 +5852,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6095,15 +5884,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122786872</v>
+        <v>122692866</v>
       </c>
       <c r="B55" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6111,21 +5895,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6135,13 +5919,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736447</v>
+        <v>736167</v>
       </c>
       <c r="R55" t="n">
-        <v>7413232</v>
+        <v>7413025</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6165,17 +5949,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6202,15 +5981,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122786888</v>
+        <v>122692867</v>
       </c>
       <c r="B56" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,24 +6009,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736358</v>
+        <v>736165</v>
       </c>
       <c r="R56" t="n">
-        <v>7413327</v>
+        <v>7413161</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6276,17 +6046,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Par</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6313,15 +6078,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122786874</v>
+        <v>122786888</v>
       </c>
       <c r="B57" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6329,34 +6089,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sarkavare, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>736381</v>
+        <v>736358</v>
       </c>
       <c r="R57" t="n">
-        <v>7413321</v>
+        <v>7413327</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6393,7 +6157,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Par</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6420,15 +6184,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122786871</v>
+        <v>122692877</v>
       </c>
       <c r="B58" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6436,21 +6195,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103022</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6460,13 +6219,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>736468</v>
+        <v>736170</v>
       </c>
       <c r="R58" t="n">
-        <v>7413177</v>
+        <v>7413160</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6490,17 +6249,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Över 20 ringhack</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6527,15 +6281,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122786873</v>
+        <v>122692876</v>
       </c>
       <c r="B59" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6543,16 +6292,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6567,13 +6316,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>736260</v>
+        <v>736253</v>
       </c>
       <c r="R59" t="n">
-        <v>7413219</v>
+        <v>7413052</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6597,17 +6346,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Flera rader ringhack</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6634,15 +6378,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122800283</v>
+        <v>122786904</v>
       </c>
       <c r="B60" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6650,16 +6389,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6674,10 +6413,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>736133</v>
+        <v>736358</v>
       </c>
       <c r="R60" t="n">
-        <v>7412935</v>
+        <v>7413327</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6736,15 +6475,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122800284</v>
+        <v>122692874</v>
       </c>
       <c r="B61" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6752,21 +6486,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6776,13 +6510,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>736110</v>
+        <v>736203</v>
       </c>
       <c r="R61" t="n">
-        <v>7413053</v>
+        <v>7412940</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6806,12 +6540,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6820,6 +6554,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49479-2024 artfynd.xlsx
+++ b/artfynd/A 49479-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692886</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692887</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692889</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692890</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692891</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692892</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692893</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692895</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692896</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692897</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692899</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692900</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692901</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692902</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692903</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692904</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692905</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692913</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692914</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2817,6 +2927,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692915</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692916</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786919</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786920</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786921</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786922</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786923</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692879</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3596,6 +3746,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692880</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3698,6 +3853,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692868</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3795,6 +3955,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786896</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3892,6 +4057,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122800283</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3989,6 +4159,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122800284</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4086,6 +4261,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692850</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4183,6 +4363,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692851</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4280,6 +4465,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692852</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4377,6 +4567,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692853</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4474,6 +4669,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692855</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4571,6 +4771,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692856</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4673,6 +4878,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786871</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4775,6 +4985,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786872</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4877,6 +5092,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786873</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4979,6 +5199,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786874</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5076,6 +5301,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692859</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5178,6 +5408,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692860</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5275,6 +5510,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692861</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5377,6 +5617,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692862</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5479,6 +5724,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692863</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5581,6 +5831,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692908</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5687,6 +5942,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786887</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5784,6 +6044,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692864</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5881,6 +6146,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692865</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5978,6 +6248,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692866</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6075,6 +6350,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692867</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6181,6 +6461,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786888</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6278,6 +6563,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692877</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6375,6 +6665,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692876</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6472,6 +6767,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786904</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6570,8 +6870,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692874</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>